--- a/classificador/dados/farma_siglas_laboratorios.xlsx
+++ b/classificador/dados/farma_siglas_laboratorios.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Siglas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Siglas'!$A$1:$E$1405</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Siglas'!$A$1:$E$1395</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1405"/>
+  <dimension ref="A1:E1395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19436,12 +19436,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>DOI</t>
+          <t>DOO</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>DOMINA FARMA</t>
+          <t>DOCTOR DAY</t>
         </is>
       </c>
       <c r="C769" t="n">
@@ -19461,12 +19461,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>DOR</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>DOCTOR DAY</t>
+          <t>DOUTORZINHO</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -19486,12 +19486,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>DOR</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>DOUTORZINHO</t>
+          <t>DOCTOR BERGER DO BRASIL</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -19511,12 +19511,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>DOU</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>DOCTOR BERGER DO BRASIL</t>
+          <t>DOUTOR FLORA</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -19536,12 +19536,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>DOU</t>
+          <t>DOY</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>DOUTOR FLORA</t>
+          <t>DOYTH COSM DO BRASIL</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -19561,12 +19561,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>DOY</t>
+          <t>DRA</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>DOYTH COSM DO BRASIL</t>
+          <t>DROGARIA ARAUJO SA</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -19586,12 +19586,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>DRA</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>DROGARIA ARAUJO SA</t>
+          <t>DROGARIA TOTAL</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -19611,12 +19611,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>DRM</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>DROGARIA MINAS BRASIL</t>
+          <t>DR MUNDIAL</t>
         </is>
       </c>
       <c r="C776" t="n">
@@ -19636,12 +19636,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>DRM</t>
+          <t>DRR</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>DR MUNDIAL</t>
+          <t>DROGARIA MINAS BRASIL</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -19661,12 +19661,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>DRR</t>
+          <t>DRV</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>DROGARIA GLOBO</t>
+          <t>DROGARIA VENANCIO</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -19686,12 +19686,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>DRT</t>
+          <t>DTO</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>DROGARIA TOTAL</t>
+          <t>DTOOLS</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -19711,12 +19711,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>DRV</t>
+          <t>DUN</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>DROGARIA VENANCIO</t>
+          <t>DUX NUTRITION</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -19736,12 +19736,12 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>DTO</t>
+          <t>DVV</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>DTOOLS</t>
+          <t>DIVINITE</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -19761,12 +19761,12 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>DUN</t>
+          <t>DYN</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>DUX NUTRITION</t>
+          <t>DYNAMIC LAB</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -19786,12 +19786,12 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>DVV</t>
+          <t>EAS</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>DIVINITE</t>
+          <t>EASE LABS</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -19811,12 +19811,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>DYN</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>DYNAMIC LAB</t>
+          <t>ECOAS</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -19836,12 +19836,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>EAS</t>
+          <t>ECC</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>EASE LABS</t>
+          <t>ECOCAPS</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -19861,12 +19861,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>EFI</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>ECOAS</t>
+          <t>EFICAZ</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -19886,12 +19886,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>EKO</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>ECOCAPS</t>
+          <t>EKOBE ESSENTIALS</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -19911,12 +19911,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>EFI</t>
+          <t>ELA</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>EFICAZ</t>
+          <t>ELANCO</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -19936,12 +19936,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>EKO</t>
+          <t>ELC</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>EKOBE ESSENTIALS</t>
+          <t>ELC</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -19961,12 +19961,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>ELA</t>
+          <t>ELE</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>ELANCO</t>
+          <t>ELEMENTOPURO</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -19986,12 +19986,12 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>EMB</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>EMBELLEZE</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -20011,12 +20011,12 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>ELE</t>
+          <t>EMI</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>ELEMENTOPURO</t>
+          <t>EMIS MINAS</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -20036,12 +20036,12 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>EMB</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>EMBELLEZE</t>
+          <t>EMANA</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -20061,12 +20061,12 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>EMI</t>
+          <t>EMP</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>EMIS MINAS</t>
+          <t>EMPORIO SEMENTE DO BEM</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -20086,12 +20086,12 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>EMANA</t>
+          <t>EMBRAS FLORA</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -20111,12 +20111,12 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>EMP</t>
+          <t>END</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>EMPORIO SEMENTE DO BEM</t>
+          <t>ENDOGEN</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -20136,12 +20136,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>EMBRAS FLORA</t>
+          <t>ENGARRAF BEBIDAS M J</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -20161,12 +20161,12 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>END</t>
+          <t>ENR</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>ENDOGEN</t>
+          <t>ENERGY UP</t>
         </is>
       </c>
       <c r="C798" t="n">
@@ -20186,12 +20186,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>EQU</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ENGARRAF BEBIDAS M J</t>
+          <t>EQUIPLEX</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -20211,12 +20211,12 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>ENR</t>
+          <t>ERG</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ENERGY UP</t>
+          <t>ERGO 30 TURBO</t>
         </is>
       </c>
       <c r="C800" t="n">
@@ -20236,12 +20236,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>EQU</t>
+          <t>ESE</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>EQUIPLEX</t>
+          <t>ESSENCE</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -20261,12 +20261,12 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>ERG</t>
+          <t>ESI</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ERGO 30 TURBO</t>
+          <t>GRUPO ESSITY</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -20286,12 +20286,12 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>ESE</t>
+          <t>ESN</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>ESSENCE</t>
+          <t>ESSENCIAL</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -20311,12 +20311,12 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>ESI</t>
+          <t>ESZ</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>GRUPO ESSITY</t>
+          <t>ESSENZA NUTRICION</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -20336,12 +20336,12 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>ESN</t>
+          <t>ETE</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>ESSENCIAL</t>
+          <t>ETERNIZE</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -20361,12 +20361,12 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>ESZ</t>
+          <t>ETI</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>ESSENZA NUTRICION</t>
+          <t>ETICOS</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -20386,12 +20386,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>ETE</t>
+          <t>ETK</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>ETERNIZE</t>
+          <t>ETIKA FARMA</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -20411,12 +20411,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>ETI</t>
+          <t>EUO</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>ETICOS</t>
+          <t>EURONUTRY</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -20436,12 +20436,12 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>ETK</t>
+          <t>EVO</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>ETIKA FARMA</t>
+          <t>EVOLABIS PROD FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="C809" t="n">
@@ -20461,12 +20461,12 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>EUO</t>
+          <t>EVR</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>EURONUTRY</t>
+          <t>EVORA NUTRICOSMETICOS</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -20486,12 +20486,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>EVO</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>EVOLABIS PROD FARMACEUTICOS LTDA</t>
+          <t>EXPRESSAO DA NATUREZA</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -20511,12 +20511,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>EVR</t>
+          <t>EXX</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EVORA NUTRICOSMETICOS</t>
+          <t>EXX NUTRITION</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -20536,12 +20536,12 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>FAA</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EXPRESSAO DA NATUREZA</t>
+          <t>FARMA FARMA</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -20561,12 +20561,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>EXX</t>
+          <t>FAB</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>EXX NUTRITION</t>
+          <t>FAB</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -20586,12 +20586,12 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>FAA</t>
+          <t>FAD</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>FARMA FARMA</t>
+          <t>FARMACIAS ASSOCIAD</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -20611,12 +20611,12 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>FAB</t>
+          <t>FAE</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>FAB</t>
+          <t>FARMACIAS OMEGA LTDA</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -20636,12 +20636,12 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>FAD</t>
+          <t>FAF</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>FARMACIAS ASSOCIAD</t>
+          <t>FARMACIAS SAO RAFAEL</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -20661,12 +20661,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>FAE</t>
+          <t>FAG</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>FARMACIAS OMEGA LTDA</t>
+          <t>GRUPO FAMIGLIA VALDUGA</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -20686,12 +20686,12 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>FAF</t>
+          <t>FAI</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>FARMACIAS SAO RAFAEL</t>
+          <t>FARMACIA E DROGARIA NISSEI</t>
         </is>
       </c>
       <c r="C819" t="n">
@@ -20711,12 +20711,12 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>FAG</t>
+          <t>FAL</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>GRUPO FAMIGLIA VALDUGA</t>
+          <t>FASLODEX</t>
         </is>
       </c>
       <c r="C820" t="n">
@@ -20736,12 +20736,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>FAI</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>FARMACIA E DROGARIA NISSEI</t>
+          <t>FARMACIA NICOLA LTDA</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -20761,12 +20761,12 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>FAL</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>FASLODEX</t>
+          <t>FARMACIA SAO JOAO</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -20786,12 +20786,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>FARMACIA NICOLA LTDA</t>
+          <t>FARMACIA PRECO MELHOR</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -20811,12 +20811,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>FAO</t>
+          <t>FAR</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>FARMACIA SAO JOAO</t>
+          <t>FABRIMED</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -20836,12 +20836,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>FAV</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>FARMACIA PRECO MELHOR</t>
+          <t>FAVO DE MEL</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -20861,12 +20861,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>FAR</t>
+          <t>FAZ</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>FABRIMED</t>
+          <t>DA FAZENDA</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -20886,12 +20886,12 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>FAV</t>
+          <t>FCF</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>FAVO DE MEL</t>
+          <t>FC FIOS E CABOS</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -20911,12 +20911,12 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>FAZ</t>
+          <t>FEL</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>DA FAZENDA</t>
+          <t>FELPS</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -20936,12 +20936,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>FCF</t>
+          <t>FEN</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>FC FIOS E CABOS</t>
+          <t>FERNANDES</t>
         </is>
       </c>
       <c r="C829" t="n">
@@ -20961,12 +20961,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>FERRING</t>
+          <t>FITO ALIM</t>
         </is>
       </c>
       <c r="C830" t="n">
@@ -20986,12 +20986,12 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>FEL</t>
+          <t>FIC</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>FELPS</t>
+          <t>FITO ESSENCIA</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -21011,12 +21011,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>FEN</t>
+          <t>FIE</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>FERNANDES</t>
+          <t>FITO ALIMENTOS</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -21036,12 +21036,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>FII</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>FITO ALIM</t>
+          <t>FIGUI FORTE</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -21061,12 +21061,12 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>FITO ESSENCIA</t>
+          <t>FINAFLEX</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -21086,12 +21086,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>FIE</t>
+          <t>FIO</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>FITO ALIMENTOS</t>
+          <t>FIOVIT</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -21111,12 +21111,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>FII</t>
+          <t>FIP</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>FIGUI FORTE</t>
+          <t>FITOPLANT</t>
         </is>
       </c>
       <c r="C836" t="n">
@@ -21136,12 +21136,12 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FIR</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>FINAFLEX</t>
+          <t>FITO NATURAIS</t>
         </is>
       </c>
       <c r="C837" t="n">
@@ -21161,12 +21161,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>FIO</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>FIOVIT</t>
+          <t>FISIOFORT NUTRITION</t>
         </is>
       </c>
       <c r="C838" t="n">
@@ -21186,12 +21186,12 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>FIP</t>
+          <t>FIV</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>FITOPLANT</t>
+          <t>FITOVIVA</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -21211,12 +21211,12 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>FIR</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>FITO NATURAIS</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="C840" t="n">
@@ -21236,12 +21236,12 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>FL7</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>FISIOFORT NUTRITION</t>
+          <t>FLORA 7 ERVAS</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -21261,12 +21261,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>FIV</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>FITOVIVA</t>
+          <t>FLAMIN MINERACAO</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -21286,12 +21286,12 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>FLC</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>FLORA NECTAR</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -21311,12 +21311,12 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>FL7</t>
+          <t>FLE</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>FLORA 7 ERVAS</t>
+          <t>FLORA ERVAS</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -21336,12 +21336,12 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>FLI</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>FLAMIN MINERACAO</t>
+          <t>FLORAVIDA</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -21361,12 +21361,12 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>FLC</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>FLORA NECTAR</t>
+          <t>FLOR E MATTOS</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -21386,12 +21386,12 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>FLE</t>
+          <t>FLP</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>FLORA ERVAS</t>
+          <t>FLORA PURA</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -21411,12 +21411,12 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>FLI</t>
+          <t>FLR</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>FLORAVIDA</t>
+          <t>FLOR DO SERTAO</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -21436,12 +21436,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>FLS</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>FLOR E MATTOS</t>
+          <t>FLORISMEL</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -21461,12 +21461,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>FLP</t>
+          <t>FLT</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>FLORA PURA</t>
+          <t>FLORA NATIVA</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -21486,12 +21486,12 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>FLR</t>
+          <t>FLV</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>FLOR DO SERTAO</t>
+          <t>FLORA VIDA</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -21511,12 +21511,12 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>FLS</t>
+          <t>FOA</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>FLORISMEL</t>
+          <t>FORTMASTER</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -21536,12 +21536,12 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>FLT</t>
+          <t>FOF</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>FLORA NATIVA</t>
+          <t>FOFEX IND DE PAPEIS</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -21561,12 +21561,12 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>FLV</t>
+          <t>FOH</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>FLORA VIDA</t>
+          <t>FORHEALTH</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -21586,12 +21586,12 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>FOA</t>
+          <t>FOI</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>FORTMASTER</t>
+          <t>FORLIFE</t>
         </is>
       </c>
       <c r="C855" t="n">
@@ -21611,12 +21611,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>FOL</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>FOFEX IND DE PAPEIS</t>
+          <t>FORHELTH NUTRICIONAL EIRELI</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -21636,12 +21636,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>FOH</t>
+          <t>FOM</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>FORHEALTH</t>
+          <t>FORTMARCAS</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -21661,12 +21661,12 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>FOI</t>
+          <t>FON</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>FORLIFE</t>
+          <t>FONTE VERDE NATURALLE</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -21686,12 +21686,12 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>FOO</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>FORHELTH NUTRICIONAL EIRELI</t>
+          <t>FOOD BRANDS IND DE PROD ALIM S A</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -21711,12 +21711,12 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>FOM</t>
+          <t>FOT</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>FORTMARCAS</t>
+          <t>FORTEPLUS</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -21736,12 +21736,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>FON</t>
+          <t>FOV</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>FONTE VERDE NATURALLE</t>
+          <t>FORTVIGOR</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -21761,12 +21761,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>FOO</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>FOOD BRANDS IND DE PROD ALIM S A</t>
+          <t>GRUPO FORTFLEX</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -21786,12 +21786,12 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>FOT</t>
+          <t>FPP</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>FORTEPLUS</t>
+          <t>FPP FRANCHISING LTDA</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -21811,12 +21811,12 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>FOV</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>FORTVIGOR</t>
+          <t>FRANCEFARMA COSMETICOS</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -21836,12 +21836,12 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>GRUPO FORTFLEX</t>
+          <t>FREEBRANDS</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -21861,12 +21861,12 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>FPP</t>
+          <t>FRI</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>FPP FRANCHISING LTDA</t>
+          <t>FRESENIUS KABI</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -21886,12 +21886,12 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>FRN</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>FRANCEFARMA COSMETICOS</t>
+          <t>FRANCHISING BRASIL FARMA</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -21911,12 +21911,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>FRR</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>FREEBRANDS</t>
+          <t>FARMARCAS</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -21936,12 +21936,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>FRI</t>
+          <t>FTT</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>FRESENIUS KABI</t>
+          <t>FITOBEL</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -21961,12 +21961,12 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>FRN</t>
+          <t>FUE</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>FRANCHISING BRASIL FARMA</t>
+          <t>FUSELABS</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -21986,12 +21986,12 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>FRR</t>
+          <t>FUS</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>FARMARCAS</t>
+          <t>FUSEFIT</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -22011,12 +22011,12 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>FTT</t>
+          <t>GAD</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>FITOBEL</t>
+          <t>GADOR DO BRASIL</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -22036,12 +22036,12 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>FUE</t>
+          <t>GAI</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>FUSELABS</t>
+          <t>GALILEO HEATH</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -22061,12 +22061,12 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>FUS</t>
+          <t>GAO</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>FUSEFIT</t>
+          <t>GABONI PROFESSIONAL</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -22086,12 +22086,12 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>GAD</t>
+          <t>GAR</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>GADOR DO BRASIL</t>
+          <t>GARBIN COSMETICO</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -22111,12 +22111,12 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>GAI</t>
+          <t>GAU</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>GALILEO HEATH</t>
+          <t>GAUCHAFARMA</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -22136,12 +22136,12 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>GAO</t>
+          <t>GEA</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>GABONI PROFESSIONAL</t>
+          <t>GENACOL</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -22161,12 +22161,12 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>GAR</t>
+          <t>GEC</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>GARBIN COSMETICO</t>
+          <t>GERACAO SAUDE RS</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -22186,12 +22186,12 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>GAU</t>
+          <t>GED</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>GAUCHAFARMA</t>
+          <t>GEDEON</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -22211,12 +22211,12 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>GEA</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>GENACOL</t>
+          <t>GERMINA PRODUTOS NATURAIS</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -22236,12 +22236,12 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>GEC</t>
+          <t>GEM</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>GERACAO SAUDE RS</t>
+          <t>GENOMMA LAB</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -22261,12 +22261,12 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>GED</t>
+          <t>GIE</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>GEDEON</t>
+          <t>GILEAD SCIENCES</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -22286,12 +22286,12 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>GIR</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>GERMINA PRODUTOS NATURAIS</t>
+          <t>GIROIL</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -22311,12 +22311,12 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>GEM</t>
+          <t>GIV</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>GENOMMA LAB</t>
+          <t>IND E COM GIVANKLIFF</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -22336,12 +22336,12 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>GIE</t>
+          <t>GLB</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>GILEAD SCIENCES</t>
+          <t>GLOBAL MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -22361,12 +22361,12 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>GON</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>GIROIL</t>
+          <t>GONUTRI</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -22386,12 +22386,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>GIV</t>
+          <t>GOO</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>IND E COM GIVANKLIFF</t>
+          <t>GLOBO PHARMA</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -22411,12 +22411,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>GLB</t>
+          <t>GPZ</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>GLOBAL MEDICAMENTOS</t>
+          <t>GPZ</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -22436,12 +22436,12 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>GOM</t>
+          <t>GRA</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>GOMES SUPLEMENTOS ALIMENTARES LTDA</t>
+          <t>GRANI AMICI</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -22461,12 +22461,12 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>GON</t>
+          <t>GRE</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>GONUTRI</t>
+          <t>GREEN IND E COM DE HIGIENE</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -22486,12 +22486,12 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>GOO</t>
+          <t>GRG</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>GLOBO PHARMA</t>
+          <t>GRINGS ALIMENTOS SAUDAVEIS</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -22511,12 +22511,12 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>GPZ</t>
+          <t>GRI</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>GPZ</t>
+          <t>GRIFFUS</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -22536,12 +22536,12 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>GRA</t>
+          <t>GRL</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>GRANI AMICI</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="C893" t="n">
@@ -22561,12 +22561,12 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>GRE</t>
+          <t>GRN</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>GREEN IND E COM DE HIGIENE</t>
+          <t>GREENSPRAY</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -22586,12 +22586,12 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>GRG</t>
+          <t>GRW</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>GRINGS ALIMENTOS SAUDAVEIS</t>
+          <t>GROW</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -22611,12 +22611,12 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>GRI</t>
+          <t>GSG</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>GRIFFUS</t>
+          <t>GSG NUTRICAO</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -22636,12 +22636,12 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>GRL</t>
+          <t>GUA</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>GUARACAMP</t>
         </is>
       </c>
       <c r="C897" t="n">
@@ -22661,12 +22661,12 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>GRN</t>
+          <t>GUD</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>GREENSPRAY</t>
+          <t>GUDAY PRODUTOS ALIMENTICIOS LTDA</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -22686,12 +22686,12 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>GRW</t>
+          <t>GUE</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>GROW</t>
+          <t>GU ENERGY LABS</t>
         </is>
       </c>
       <c r="C899" t="n">
@@ -22711,12 +22711,12 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>GSG</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>GSG NUTRICAO</t>
+          <t>GUMMY VITAMINAS</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -22736,12 +22736,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>GUA</t>
+          <t>GVI</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>GUARACAMP</t>
+          <t>GVIT</t>
         </is>
       </c>
       <c r="C901" t="n">
@@ -22761,12 +22761,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>GUD</t>
+          <t>GZT</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>GUDAY PRODUTOS ALIMENTICIOS LTDA</t>
+          <t>GZT COM IMP S A</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -22786,12 +22786,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>GUE</t>
+          <t>HED</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>GU ENERGY LABS</t>
+          <t>HEDERA</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -22811,12 +22811,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>HEF</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>GUMMY VITAMINAS</t>
+          <t>HEMAFARMA</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -22836,12 +22836,12 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>GVI</t>
+          <t>HEK</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>GVIT</t>
+          <t>HENKEL</t>
         </is>
       </c>
       <c r="C905" t="n">
@@ -22861,12 +22861,12 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>GZT</t>
+          <t>HEO</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>GZT COM IMP S A</t>
+          <t>HELOFARMA</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -22886,12 +22886,12 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>HED</t>
+          <t>HEP</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>HEDERA</t>
+          <t>HEPANEW</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -22911,12 +22911,12 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>HEF</t>
+          <t>HES</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>HEMAFARMA</t>
+          <t>HERUSZEUS SUPLEMENTOS</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -22936,12 +22936,12 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>HEK</t>
+          <t>HET</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>HENKEL</t>
+          <t>HEALTHPLANT</t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -22961,12 +22961,12 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>HEO</t>
+          <t>HEU</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>HELOFARMA</t>
+          <t>HERBANATUS</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -22986,12 +22986,12 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>HEP</t>
+          <t>HEV</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>HEPANEW</t>
+          <t>HELAVEN</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -23011,12 +23011,12 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>HES</t>
+          <t>HIE</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>HERUSZEUS SUPLEMENTOS</t>
+          <t>HIPERPLUS</t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -23036,12 +23036,12 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>HIL</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>HEALTHPLANT</t>
+          <t>HILE INDUSTRIA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -23061,12 +23061,12 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>HEU</t>
+          <t>HOI</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>HERBANATUS</t>
+          <t>HORIZONTE ALIMENTOS</t>
         </is>
       </c>
       <c r="C914" t="n">
@@ -23086,12 +23086,12 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>HEV</t>
+          <t>HOR</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>HELAVEN</t>
+          <t>HORIZONTE</t>
         </is>
       </c>
       <c r="C915" t="n">
@@ -23111,12 +23111,12 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>HIE</t>
+          <t>HOT</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>HIPERPLUS</t>
+          <t>HOT BUTTERED</t>
         </is>
       </c>
       <c r="C916" t="n">
@@ -23136,12 +23136,12 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>HIL</t>
+          <t>HRR</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>HILE INDUSTRIA DE ALIMENTOS LTDA</t>
+          <t>HERBARO</t>
         </is>
       </c>
       <c r="C917" t="n">
@@ -23161,12 +23161,12 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>HOI</t>
+          <t>HRT</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>HORIZONTE ALIMENTOS</t>
+          <t>HERTZ</t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -23186,12 +23186,12 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>HOR</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>HORIZONTE</t>
+          <t>HERVAS BRASIL</t>
         </is>
       </c>
       <c r="C919" t="n">
@@ -23211,12 +23211,12 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>HOT</t>
+          <t>HYE</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>HOT BUTTERED</t>
+          <t>HYPERNATUS</t>
         </is>
       </c>
       <c r="C920" t="n">
@@ -23236,12 +23236,12 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>HRR</t>
+          <t>IBL</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>HERBARO</t>
+          <t>IBL INDUSTRIA LTDA</t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -23261,12 +23261,12 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>HRT</t>
+          <t>IDE</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>HERTZ</t>
+          <t>IDEAL COSMETICOS</t>
         </is>
       </c>
       <c r="C922" t="n">
@@ -23286,12 +23286,12 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>IDL</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>HERVAS BRASIL</t>
+          <t>IDNLABS</t>
         </is>
       </c>
       <c r="C923" t="n">
@@ -23311,12 +23311,12 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>HYE</t>
+          <t>IFB</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>HYPERNATUS</t>
+          <t>IFBRASIL</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -23336,12 +23336,12 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>IBL</t>
+          <t>IMU</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>IBL INDUSTRIA LTDA</t>
+          <t>IMUNE HAIR</t>
         </is>
       </c>
       <c r="C925" t="n">
@@ -23361,12 +23361,12 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>IDE</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>IDEAL COSMETICOS</t>
+          <t>INDAFARMA</t>
         </is>
       </c>
       <c r="C926" t="n">
@@ -23386,12 +23386,12 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>IDL</t>
+          <t>INB</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>IDNLABS</t>
+          <t>INBEAUTY</t>
         </is>
       </c>
       <c r="C927" t="n">
@@ -23411,12 +23411,12 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>IFB</t>
+          <t>INE</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>IFBRASIL</t>
+          <t>INDS REUNIDAS RAYMUNDO FONTE</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -23436,12 +23436,12 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>IMU</t>
+          <t>INH</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>IMUNE HAIR</t>
+          <t>INR HEALTH</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -23461,12 +23461,12 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>INA</t>
+          <t>INI</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>INDAFARMA</t>
+          <t>INDIANA</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -23486,12 +23486,12 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>INB</t>
+          <t>INM</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>INBEAUTY</t>
+          <t>INTENSE CARE COSMETICOS</t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -23511,12 +23511,12 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>INE</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>INDS REUNIDAS RAYMUNDO FONTE</t>
+          <t>INFA INST FARMA PERFECT LTDA</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -23536,12 +23536,12 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>INH</t>
+          <t>INO</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>INR HEALTH</t>
+          <t>INOAR</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -23561,12 +23561,12 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>INI</t>
+          <t>INU</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>INDIANA</t>
+          <t>INDUSMED MEDICAMENTOS E SUPLEMENTOS</t>
         </is>
       </c>
       <c r="C934" t="n">
@@ -23586,12 +23586,12 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>INM</t>
+          <t>INV</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>INTENSE CARE COSMETICOS</t>
+          <t>INOVAMIX</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -23611,12 +23611,12 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>INN</t>
+          <t>INY</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>INFA INST FARMA PERFECT LTDA</t>
+          <t>INTENSY</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -23636,12 +23636,12 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>INO</t>
+          <t>IOO</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>INOAR</t>
+          <t>INOVE</t>
         </is>
       </c>
       <c r="C937" t="n">
@@ -23661,12 +23661,12 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>INU</t>
+          <t>IPE</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>INDUSMED MEDICAMENTOS E SUPLEMENTOS</t>
+          <t>IPSEN SA</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -23686,12 +23686,12 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>INV</t>
+          <t>IPN</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>INOVAMIX</t>
+          <t>IPAN NUTRITION</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -23711,12 +23711,12 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>INY</t>
+          <t>IRE</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>INTENSY</t>
+          <t>IREMAR ALIMENTOS</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -23736,12 +23736,12 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>IOO</t>
+          <t>IRI</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>INOVE</t>
+          <t>IRIDIUM LABS</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -23761,12 +23761,12 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>IPE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>IPSEN SA</t>
+          <t>ITA BRASIL</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -23786,12 +23786,12 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>IPN</t>
+          <t>ITL</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>IPAN NUTRITION</t>
+          <t>ITALLIAN HAIRTECH</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -23811,12 +23811,12 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>IRE</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>IREMAR ALIMENTOS</t>
+          <t>INTERCRON</t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -23836,12 +23836,12 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>IRI</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>IRIDIUM LABS</t>
+          <t>JACQUES JANINE</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -23861,12 +23861,12 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAS</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>ITA BRASIL</t>
+          <t>JA SAUDE ANIMAL</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -23886,12 +23886,12 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>ITL</t>
+          <t>JBP</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>ITALLIAN HAIRTECH</t>
+          <t>J B PRODUTOS NATURAIS LTDA ME</t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -23911,12 +23911,12 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>JPP</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>INTERCRON</t>
+          <t>JP PEREIRA</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -23936,12 +23936,12 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>JAC</t>
+          <t>JUN</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>JACQUES JANINE</t>
+          <t>JUNCO</t>
         </is>
       </c>
       <c r="C949" t="n">
@@ -23961,12 +23961,12 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>JAS</t>
+          <t>KAI</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>JA SAUDE ANIMAL</t>
+          <t>KANIRIM</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -23986,12 +23986,12 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>JBP</t>
+          <t>KAM</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>J B PRODUTOS NATURAIS LTDA ME</t>
+          <t>KAMPO DE ERVAS</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -24011,12 +24011,12 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>JPP</t>
+          <t>KAR</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>JP PEREIRA</t>
+          <t>KARSTEN TEXTIL</t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -24036,12 +24036,12 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>JUN</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>JUNCO</t>
+          <t>KELLDRIN IND COM PROD QUIM</t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -24061,12 +24061,12 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>KAI</t>
+          <t>KER</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>KANIRIM</t>
+          <t>KERABRASIL</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -24086,12 +24086,12 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>KAM</t>
+          <t>KET</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>KAMPO DE ERVAS</t>
+          <t>KERT IND E COM DE COSMETICOS</t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -24111,12 +24111,12 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>KAR</t>
+          <t>KEU</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>KARSTEN TEXTIL</t>
+          <t>KEUNE HAIRCOSMETICS</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -24136,12 +24136,12 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>KLY</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>KELLDRIN IND COM PROD QUIM</t>
+          <t>KLEY HERTZ</t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -24161,12 +24161,12 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>KER</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>KERABRASIL</t>
+          <t>KNUT</t>
         </is>
       </c>
       <c r="C958" t="n">
@@ -24186,12 +24186,12 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>KET</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>KERT IND E COM DE COSMETICOS</t>
+          <t>KODILAR</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -24211,12 +24211,12 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>KEU</t>
+          <t>KOK</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>KEUNE HAIRCOSMETICS</t>
+          <t>KOKE PARTNERS</t>
         </is>
       </c>
       <c r="C960" t="n">
@@ -24236,12 +24236,12 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>KLY</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>KLEY HERTZ</t>
+          <t>KORIN CIA</t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -24261,12 +24261,12 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>KNUT</t>
+          <t>KRENAK DO BRASIL</t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -24286,12 +24286,12 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>KRR</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>KODILAR</t>
+          <t>KARTTI</t>
         </is>
       </c>
       <c r="C963" t="n">
@@ -24311,12 +24311,12 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>KOK</t>
+          <t>KRS</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>KOKE PARTNERS</t>
+          <t>KRESS</t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -24336,12 +24336,12 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>KTG</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>KORIN CIA</t>
+          <t>KTG NUTRICIONAL</t>
         </is>
       </c>
       <c r="C965" t="n">
@@ -24361,12 +24361,12 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>KRENAK DO BRASIL</t>
+          <t>LA SAN DAY PHARMA</t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -24386,12 +24386,12 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>KRR</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>KARTTI</t>
+          <t>LAB IND FARMACEUTICO</t>
         </is>
       </c>
       <c r="C967" t="n">
@@ -24411,12 +24411,12 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>KRS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>KRESS</t>
+          <t>LACERDA E SA LTDA</t>
         </is>
       </c>
       <c r="C968" t="n">
@@ -24436,12 +24436,12 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>KTG</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>KTG NUTRICIONAL</t>
+          <t>LANDERLABS</t>
         </is>
       </c>
       <c r="C969" t="n">
@@ -24461,12 +24461,12 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAE</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>LA SAN DAY PHARMA</t>
+          <t>LAPERFI</t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -24486,12 +24486,12 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LAF</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>LAB IND FARMACEUTICO</t>
+          <t>LAFARE</t>
         </is>
       </c>
       <c r="C971" t="n">
@@ -24511,12 +24511,12 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAH</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>LACERDA E SA LTDA</t>
+          <t>LABORATORIO LAHAS</t>
         </is>
       </c>
       <c r="C972" t="n">
@@ -24536,12 +24536,12 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAI</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>LANDERLABS</t>
+          <t>LATICINIOS BELA VISTA LTDA</t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -24561,12 +24561,12 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>LAE</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>LAPERFI</t>
+          <t>LABMUSA</t>
         </is>
       </c>
       <c r="C974" t="n">
@@ -24586,12 +24586,12 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>LAF</t>
+          <t>LAO</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>LAFARE</t>
+          <t>LABOR QUIMICA ALQUIMIA</t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -24611,12 +24611,12 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>LAH</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>LABORATORIO LAHAS</t>
+          <t>LABORATIL</t>
         </is>
       </c>
       <c r="C976" t="n">
@@ -24636,12 +24636,12 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>LAI</t>
+          <t>LAV</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>LABORATIL</t>
+          <t>LABOVET</t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -24661,12 +24661,12 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>LAPERLI</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="C978" t="n">
@@ -24686,12 +24686,12 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>LEA</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>LABMUSA</t>
+          <t>LE ANGE COSMETICOS</t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -24711,12 +24711,12 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>LAO</t>
+          <t>LEO</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>LABOGAN</t>
+          <t>LEO PHARMA</t>
         </is>
       </c>
       <c r="C980" t="n">
@@ -24736,12 +24736,12 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>LER</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>LABOR QUIMICA ALQUIMIA</t>
+          <t>LEGRAND PHARMA</t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -24761,12 +24761,12 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>LAV</t>
+          <t>LIA</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>LABOVET</t>
+          <t>LIVVA</t>
         </is>
       </c>
       <c r="C982" t="n">
@@ -24786,12 +24786,12 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>LBS</t>
+          <t>LIE</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>LBS</t>
+          <t>LIFE DROGAMAIS</t>
         </is>
       </c>
       <c r="C983" t="n">
@@ -24811,12 +24811,12 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>LEA</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>LE ANGE COSMETICOS</t>
+          <t>LIMA E PERGHER</t>
         </is>
       </c>
       <c r="C984" t="n">
@@ -24836,12 +24836,12 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>LEO</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>LEO PHARMA</t>
+          <t>LINEA ALIMENTOS</t>
         </is>
       </c>
       <c r="C985" t="n">
@@ -24861,12 +24861,12 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>LER</t>
+          <t>LIQ</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>LEGRAND PHARMA</t>
+          <t>LIQUIDZ</t>
         </is>
       </c>
       <c r="C986" t="n">
@@ -24886,12 +24886,12 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>LIA</t>
+          <t>LIV</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>LIVVA</t>
+          <t>LIVER COSMETICOS</t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -24911,12 +24911,12 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>LIE</t>
+          <t>LOC</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>LIFE DROGAMAIS</t>
+          <t>LOCKO SUPLEMENTOS</t>
         </is>
       </c>
       <c r="C988" t="n">
@@ -24936,12 +24936,12 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>LOG</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>LIMA E PERGHER</t>
+          <t>LONGEVITA HIGIENICOS</t>
         </is>
       </c>
       <c r="C989" t="n">
@@ -24961,12 +24961,12 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>LOJ</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>LINEA ALIMENTOS</t>
+          <t>LOJAS REDE COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="C990" t="n">
@@ -24986,12 +24986,12 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>LIQ</t>
+          <t>LON</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>LIQUIDZ</t>
+          <t>LONGA</t>
         </is>
       </c>
       <c r="C991" t="n">
@@ -25011,12 +25011,12 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>LIV</t>
+          <t>LOR</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>LIVER COSMETICOS</t>
+          <t>LOREAL</t>
         </is>
       </c>
       <c r="C992" t="n">
@@ -25036,12 +25036,12 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>LOC</t>
+          <t>LOU</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>LOCKO SUPLEMENTOS</t>
+          <t>LOURO VERDE</t>
         </is>
       </c>
       <c r="C993" t="n">
@@ -25061,12 +25061,12 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>LOG</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>LONGEVITA HIGIENICOS</t>
+          <t>LOWELL</t>
         </is>
       </c>
       <c r="C994" t="n">
@@ -25086,12 +25086,12 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>LOJ</t>
+          <t>LOZ</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>LOJAS REDE COMERCIAL LTDA</t>
+          <t>LOZZANO COSMETICOS EIRELI</t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -25111,12 +25111,12 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>LON</t>
+          <t>LRR</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>LONGA</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="C996" t="n">
@@ -25136,12 +25136,12 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>LOR</t>
+          <t>LUB</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>LOREAL</t>
+          <t>LUBRIS</t>
         </is>
       </c>
       <c r="C997" t="n">
@@ -25161,12 +25161,12 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>LOU</t>
+          <t>LUG</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>LOURO VERDE</t>
+          <t>LUGEN</t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -25186,12 +25186,12 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LUI</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>LOWELL</t>
+          <t>LUNIS</t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -25211,12 +25211,12 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>LOZ</t>
+          <t>LUP</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>LOZZANO COSMETICOS EIRELI</t>
+          <t>LUPUS ALIMENTOS</t>
         </is>
       </c>
       <c r="C1000" t="n">
@@ -25236,12 +25236,12 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>LRR</t>
+          <t>LVV</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>LAVIVE COSMETICOS</t>
         </is>
       </c>
       <c r="C1001" t="n">
@@ -25261,12 +25261,12 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>LTT</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>LATICINIOS BELA VISTA LTDA</t>
+          <t>MAGARAZ</t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -25286,12 +25286,12 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>LUB</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>LUBRIS</t>
+          <t>MADREVITA</t>
         </is>
       </c>
       <c r="C1003" t="n">
@@ -25311,12 +25311,12 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>LUG</t>
+          <t>MAF</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>LUGEN</t>
+          <t>MAKROFARMA</t>
         </is>
       </c>
       <c r="C1004" t="n">
@@ -25336,12 +25336,12 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>LUI</t>
+          <t>MAH</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>LUNIS</t>
+          <t>MARIAH COSM</t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -25361,12 +25361,12 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>LUP</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>LUPUS ALIMENTOS</t>
+          <t>LAB FARMACEUTICO DA MARINHA</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -25386,12 +25386,12 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>LVV</t>
+          <t>MAK</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>LAVIVE COSMETICOS</t>
+          <t>MAKRO</t>
         </is>
       </c>
       <c r="C1007" t="n">
@@ -25411,12 +25411,12 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MAL</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>MAGARAZ</t>
+          <t>MACROCELL</t>
         </is>
       </c>
       <c r="C1008" t="n">
@@ -25436,12 +25436,12 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>MAM</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>MADREVITA</t>
+          <t>MAMBO</t>
         </is>
       </c>
       <c r="C1009" t="n">
@@ -25461,12 +25461,12 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>MAF</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>MAKROFARMA</t>
+          <t>MACPAUL</t>
         </is>
       </c>
       <c r="C1010" t="n">
@@ -25486,12 +25486,12 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>MAH</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>MARIAH COSM</t>
+          <t>MARTINS COM SERV DISTRIB</t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -25511,12 +25511,12 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>MAU</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>LAB FARMACEUTICO DA MARINHA</t>
+          <t>MASTERWAY SUPLEMENTOS</t>
         </is>
       </c>
       <c r="C1012" t="n">
@@ -25536,12 +25536,12 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>MAK</t>
+          <t>MAV</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>MAKRO</t>
+          <t>MARVALE</t>
         </is>
       </c>
       <c r="C1013" t="n">
@@ -25561,12 +25561,12 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>MAL</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>MACROCELL</t>
+          <t>MCD MIAMI COSMETIC</t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -25586,12 +25586,12 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>MAM</t>
+          <t>MCS</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>MAMBO</t>
+          <t>MCG SUPLEMENTOS ALIMENTARES</t>
         </is>
       </c>
       <c r="C1015" t="n">
@@ -25611,12 +25611,12 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>MEA</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>MACPAUL</t>
+          <t>MEDNA FARMACEUTICA</t>
         </is>
       </c>
       <c r="C1016" t="n">
@@ -25636,12 +25636,12 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>MEB</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>MARTINS COM SERV DISTRIB</t>
+          <t>MELBRAS</t>
         </is>
       </c>
       <c r="C1017" t="n">
@@ -25661,12 +25661,12 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>MAU</t>
+          <t>MEF</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>MASTERWAY SUPLEMENTOS</t>
+          <t>MELFORT</t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -25686,12 +25686,12 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>MAV</t>
+          <t>MEI</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>MARVALE</t>
+          <t>MEDICAPS</t>
         </is>
       </c>
       <c r="C1019" t="n">
@@ -25711,12 +25711,12 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>MEK</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>MCD MIAMI COSMETIC</t>
+          <t>MERAKI ALIMENTOS</t>
         </is>
       </c>
       <c r="C1020" t="n">
@@ -25736,12 +25736,12 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>MEL</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>MCG SUPLEMENTOS ALIMENTARES</t>
+          <t>MEL DO SOL</t>
         </is>
       </c>
       <c r="C1021" t="n">
@@ -25761,12 +25761,12 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>MEA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>MEDNA FARMACEUTICA</t>
+          <t>MEU MEL</t>
         </is>
       </c>
       <c r="C1022" t="n">
@@ -25786,12 +25786,12 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>MELBRAS</t>
+          <t>MEDCNUTRY</t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -25811,12 +25811,12 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>MEF</t>
+          <t>MEO</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>MELFORT</t>
+          <t>MEDTRONIC</t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -25836,12 +25836,12 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>MEI</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>MEDICAPS</t>
+          <t>MELCOPROL</t>
         </is>
       </c>
       <c r="C1025" t="n">
@@ -25861,12 +25861,12 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>MEK</t>
+          <t>MEU</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>MERAKI ALIMENTOS</t>
+          <t>METAPLUS</t>
         </is>
       </c>
       <c r="C1026" t="n">
@@ -25886,12 +25886,12 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>MEL</t>
+          <t>MEW</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>MEL DO SOL</t>
+          <t>MEL WENZEL IND COM LTDA</t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -25911,12 +25911,12 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>MEU MEL</t>
+          <t>MEDIX BRASIL</t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -25936,12 +25936,12 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>MEN</t>
+          <t>MEZ</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>MEDCNUTRY</t>
+          <t>MEIZLER UCB</t>
         </is>
       </c>
       <c r="C1029" t="n">
@@ -25961,12 +25961,12 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>MEO</t>
+          <t>MFF</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>MEDTRONIC</t>
+          <t>MFF RUETTE</t>
         </is>
       </c>
       <c r="C1030" t="n">
@@ -25986,12 +25986,12 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>MEP</t>
+          <t>MGG</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>MELCOPROL</t>
+          <t>MCG</t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -26011,12 +26011,12 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>MEU</t>
+          <t>MIC</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>MEQQUIMICA</t>
+          <t>MICREX</t>
         </is>
       </c>
       <c r="C1032" t="n">
@@ -26036,12 +26036,12 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>MEW</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>MEL WENZEL IND COM LTDA</t>
+          <t>MIDWAY</t>
         </is>
       </c>
       <c r="C1033" t="n">
@@ -26061,12 +26061,12 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>MEDIX BRASIL</t>
+          <t>MIX NUTRI</t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -26086,12 +26086,12 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>MEZ</t>
+          <t>MIP</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>MEIZLER UCB</t>
+          <t>MIX PERFUMARIA</t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -26111,12 +26111,12 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>MFF</t>
+          <t>MLL</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>MFF RUETTE</t>
+          <t>MELDICA</t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -26136,12 +26136,12 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>MGG</t>
+          <t>MLO</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>MCG</t>
+          <t>MELORA</t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -26161,12 +26161,12 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>MIC</t>
+          <t>MMD</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>MICREX</t>
+          <t>MM LABORATORIO DUOM</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -26186,12 +26186,12 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>MMN</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>MIDWAY</t>
+          <t>MM IND NUTRACEUTICA</t>
         </is>
       </c>
       <c r="C1039" t="n">
@@ -26211,12 +26211,12 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MNP</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>MILLER IND FARMACEUTICA</t>
+          <t>MN PROPOLIS</t>
         </is>
       </c>
       <c r="C1040" t="n">
@@ -26236,12 +26236,12 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>MIX NUTRI</t>
+          <t>MOPH DERME</t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -26261,12 +26261,12 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>MIP</t>
+          <t>MOE</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>MIX PERFUMARIA</t>
+          <t>MOEDENSE</t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -26286,12 +26286,12 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>MELDICA</t>
+          <t>MOPH</t>
         </is>
       </c>
       <c r="C1043" t="n">
@@ -26311,12 +26311,12 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>MLO</t>
+          <t>MON</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>MELORA</t>
+          <t>MONDELEZ INTL</t>
         </is>
       </c>
       <c r="C1044" t="n">
@@ -26336,12 +26336,12 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>MMD</t>
+          <t>MOR</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>MM LABORATORIO DUOM</t>
+          <t>MORO</t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -26361,12 +26361,12 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>MMN</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>MM IND NUTRACEUTICA</t>
+          <t>MONSTER BEVERAGE</t>
         </is>
       </c>
       <c r="C1046" t="n">
@@ -26386,12 +26386,12 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>MNP</t>
+          <t>MOT</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>MN PROPOLIS</t>
+          <t>MOSTEIRO DEVAKAN PRODS NAT E ALIMS LTDA</t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -26411,12 +26411,12 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>MOD</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>MOPH DERME</t>
+          <t>M LABS COMERCIO DE PRODUTOS NATURAIS</t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -26436,12 +26436,12 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>MOE</t>
+          <t>MR8</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>MOEDENSE</t>
+          <t>MR 8 DISTRIBUIDORA E COMERCIO DE SUPLEMENTO ALIMENTARES LTDA</t>
         </is>
       </c>
       <c r="C1049" t="n">
@@ -26461,12 +26461,12 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>MRC</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>MOPH</t>
+          <t>MARCIA CIA</t>
         </is>
       </c>
       <c r="C1050" t="n">
@@ -26486,12 +26486,12 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>MON</t>
+          <t>MRI</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>MONDELEZ INTL</t>
+          <t>MARIANO FARMACIAS</t>
         </is>
       </c>
       <c r="C1051" t="n">
@@ -26511,12 +26511,12 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>MOR</t>
+          <t>MRR</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>MORO</t>
+          <t>MARCFARMA</t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -26536,12 +26536,12 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>MSE</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>MONSTER BEVERAGE</t>
+          <t>MASTER ENERGY</t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -26561,12 +26561,12 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>MOT</t>
+          <t>MST</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>MOSTEIRO DEVAKAN PRODS NAT E ALIMS LTDA</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="C1054" t="n">
@@ -26586,12 +26586,12 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>M LABS COMERCIO DE PRODUTOS NATURAIS</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -26611,12 +26611,12 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>MR8</t>
+          <t>MUI</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>MR 8 DISTRIBUIDORA E COMERCIO DE SUPLEMENTO ALIMENTARES LTDA</t>
+          <t>MULTINATURE</t>
         </is>
       </c>
       <c r="C1056" t="n">
@@ -26636,12 +26636,12 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>MRC</t>
+          <t>MUN</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>MARCIA CIA</t>
+          <t>MUNDO ANIMAL</t>
         </is>
       </c>
       <c r="C1057" t="n">
@@ -26661,12 +26661,12 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>MRI</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>MARIANO FARMACIAS</t>
+          <t>MURIEL CIA</t>
         </is>
       </c>
       <c r="C1058" t="n">
@@ -26686,12 +26686,12 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>MRR</t>
+          <t>MUT</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>MARCFARMA</t>
+          <t>MULTIDROGAS</t>
         </is>
       </c>
       <c r="C1059" t="n">
@@ -26711,12 +26711,12 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>MSE</t>
+          <t>MUU</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>MASTER ENERGY</t>
+          <t>MAURO FERNANDO KONRAD</t>
         </is>
       </c>
       <c r="C1060" t="n">
@@ -26736,12 +26736,12 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>MST</t>
+          <t>MUV</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>MULTIVITTA</t>
         </is>
       </c>
       <c r="C1061" t="n">
@@ -26761,12 +26761,12 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MUW</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>METAPLUS</t>
+          <t>MUWIZ</t>
         </is>
       </c>
       <c r="C1062" t="n">
@@ -26786,12 +26786,12 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>MWA</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>M W A COM ALIMENTOS</t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -26811,12 +26811,12 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>MTT</t>
+          <t>MXI</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>METALAB</t>
+          <t>MAXIMUS</t>
         </is>
       </c>
       <c r="C1064" t="n">
@@ -26836,12 +26836,12 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>MUI</t>
+          <t>MXX</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>MULTINATURE</t>
+          <t>MAXILLURING</t>
         </is>
       </c>
       <c r="C1065" t="n">
@@ -26861,12 +26861,12 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>MUN</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>MUNDO ANIMAL</t>
+          <t>NATURALGREEN</t>
         </is>
       </c>
       <c r="C1066" t="n">
@@ -26886,12 +26886,12 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>MURIEL CIA</t>
+          <t>NATTUBRAS</t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -26911,12 +26911,12 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>MUT</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>MULTIDROGAS</t>
+          <t>NATUSDAY</t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -26936,12 +26936,12 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>MUU</t>
+          <t>NAE</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>MAURO FERNANDO KONRAD</t>
+          <t>NAT USER</t>
         </is>
       </c>
       <c r="C1069" t="n">
@@ -26961,12 +26961,12 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>MUV</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>MULTIVITTA</t>
+          <t>NATURE GOLD</t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -26986,12 +26986,12 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>MUW</t>
+          <t>NAH</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>MUWIZ</t>
+          <t>NATHUREPRO</t>
         </is>
       </c>
       <c r="C1071" t="n">
@@ -27011,12 +27011,12 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>MWA</t>
+          <t>NAI</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>M W A COM ALIMENTOS</t>
+          <t>NATIVA</t>
         </is>
       </c>
       <c r="C1072" t="n">
@@ -27036,12 +27036,12 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>MXI</t>
+          <t>NAL</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>MAXIMUS</t>
+          <t>NATURALHELF</t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -27061,12 +27061,12 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>MXX</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>MAXILLURING</t>
+          <t>NATURE CAMPOS</t>
         </is>
       </c>
       <c r="C1074" t="n">
@@ -27086,12 +27086,12 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>NAO</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>NATURALGREEN</t>
+          <t>NAXOS</t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -27111,12 +27111,12 @@
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>NATTUBRAS</t>
+          <t>NATURAL WEATHER</t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -27136,12 +27136,12 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>NAS</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>NATUSDAY</t>
+          <t>NASCILAB</t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -27161,12 +27161,12 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>NAE</t>
+          <t>NAU</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>NAT USER</t>
+          <t>CIA DA NATUREZA</t>
         </is>
       </c>
       <c r="C1078" t="n">
@@ -27186,12 +27186,12 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>NATURE GOLD</t>
+          <t>NAVILLUS</t>
         </is>
       </c>
       <c r="C1079" t="n">
@@ -27211,12 +27211,12 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>NAH</t>
+          <t>NAX</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>NATHUREPRO</t>
+          <t>NATURIX</t>
         </is>
       </c>
       <c r="C1080" t="n">
@@ -27236,12 +27236,12 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>NAI</t>
+          <t>NEA</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>NATIVA</t>
+          <t>NECTAR PLUS</t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -27261,12 +27261,12 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>NAL</t>
+          <t>NEB</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>NATURALHELF</t>
+          <t>NEW BEAUTY PROFESSIONAL</t>
         </is>
       </c>
       <c r="C1082" t="n">
@@ -27286,12 +27286,12 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>NATURE CAMPOS</t>
+          <t>NEO PREMIUM</t>
         </is>
       </c>
       <c r="C1083" t="n">
@@ -27311,12 +27311,12 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>NAO</t>
+          <t>NEI</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>NAXOS</t>
+          <t>NEW MILLEN</t>
         </is>
       </c>
       <c r="C1084" t="n">
@@ -27336,12 +27336,12 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>NEL</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>NATURAL WEATHER</t>
+          <t>NEW LIFE</t>
         </is>
       </c>
       <c r="C1085" t="n">
@@ -27361,12 +27361,12 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>NAS</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>NASCILAB</t>
+          <t>NECTAR FLORAL</t>
         </is>
       </c>
       <c r="C1086" t="n">
@@ -27386,12 +27386,12 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>NAU</t>
+          <t>NEV</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>CIA DA NATUREZA</t>
+          <t>NEW VITTA</t>
         </is>
       </c>
       <c r="C1087" t="n">
@@ -27411,12 +27411,12 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>NEX</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>NAVILLUS</t>
+          <t>NEWMIX SUPPLEMENTS</t>
         </is>
       </c>
       <c r="C1088" t="n">
@@ -27436,12 +27436,12 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>NAX</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>NATURIX</t>
+          <t>NIPOVITA</t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -27461,12 +27461,12 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>NEA</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>NECTAR PLUS</t>
+          <t>NOVATECH INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C1090" t="n">
@@ -27486,12 +27486,12 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>NEB</t>
+          <t>NOB</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>NEW BEAUTY PROFESSIONAL</t>
+          <t>NOVVO BEM ESTAR</t>
         </is>
       </c>
       <c r="C1091" t="n">
@@ -27511,12 +27511,12 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>NOH</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>NEO PREMIUM</t>
+          <t>NOHRAAN</t>
         </is>
       </c>
       <c r="C1092" t="n">
@@ -27536,12 +27536,12 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>NEI</t>
+          <t>NOO</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>NEW MILLEN</t>
+          <t>NEOPURE</t>
         </is>
       </c>
       <c r="C1093" t="n">
@@ -27561,12 +27561,12 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>NEL</t>
+          <t>NRI</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>NEW LIFE</t>
+          <t>NUTRIMAIS</t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -27586,12 +27586,12 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>NRM</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>NECTAR FLORAL</t>
+          <t>NUTRIMEL</t>
         </is>
       </c>
       <c r="C1095" t="n">
@@ -27611,12 +27611,12 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>NEV</t>
+          <t>NRR</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>NEW VITTA</t>
+          <t>NUTRILIFE</t>
         </is>
       </c>
       <c r="C1096" t="n">
@@ -27636,12 +27636,12 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>NEX</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>NEWMIX SUPPLEMENTS</t>
+          <t>NUTRILAR</t>
         </is>
       </c>
       <c r="C1097" t="n">
@@ -27661,12 +27661,12 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>NRY</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>NIPOVITA</t>
+          <t>NUTRYDERM</t>
         </is>
       </c>
       <c r="C1098" t="n">
@@ -27686,12 +27686,12 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>NTA</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>NOVATECH INDUSTRIA E COMERCIO LTDA</t>
+          <t>NUTRATA</t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -27711,12 +27711,12 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>NOB</t>
+          <t>NTE</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>NOVVO BEM ESTAR</t>
+          <t>NATURE</t>
         </is>
       </c>
       <c r="C1100" t="n">
@@ -27736,12 +27736,12 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>NOH</t>
+          <t>NTI</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>NOHRAAN</t>
+          <t>NUTRIBELLE</t>
         </is>
       </c>
       <c r="C1101" t="n">
@@ -27761,12 +27761,12 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>NOO</t>
+          <t>NTN</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>NEOPURE</t>
+          <t>NUTRITION FOR</t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -27786,12 +27786,12 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>NRI</t>
+          <t>NTO</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>NUTRIMAIS</t>
+          <t>NUTRIGOLD DO BRASIL</t>
         </is>
       </c>
       <c r="C1103" t="n">
@@ -27811,12 +27811,12 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>NRM</t>
+          <t>NTP</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>NUTRIMEL</t>
+          <t>NUTRY POWER</t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -27836,12 +27836,12 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>NRR</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>NUTRILIFE</t>
+          <t>NATURASUL</t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -27861,12 +27861,12 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>NTT</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>NUTRILAR</t>
+          <t>NATUPHITUS</t>
         </is>
       </c>
       <c r="C1106" t="n">
@@ -27886,12 +27886,12 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>NRY</t>
+          <t>NTU</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>NUTRYDERM</t>
+          <t>NATURALIS</t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -27911,12 +27911,12 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>NTA</t>
+          <t>NUB</t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>NUTRATA</t>
+          <t>NATUSBEL</t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -27936,12 +27936,12 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>NTE</t>
+          <t>NUC</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>NATURE</t>
+          <t>NUTRATEC</t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -27961,12 +27961,12 @@
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>NTI</t>
+          <t>NUD</t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>NUTRIBELLE</t>
+          <t>NUTRI WIEDER</t>
         </is>
       </c>
       <c r="C1110" t="n">
@@ -27986,12 +27986,12 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>NTN</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>NUTRITION FOR</t>
+          <t>NATUSER</t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -28011,12 +28011,12 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>NTO</t>
+          <t>NUF</t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>NUTRIGOLD DO BRASIL</t>
+          <t>NUTRAFOR</t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -28036,12 +28036,12 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>NTP</t>
+          <t>NUG</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>NUTRY POWER</t>
+          <t>NUTRIGEN</t>
         </is>
       </c>
       <c r="C1113" t="n">
@@ -28061,12 +28061,12 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>NUH</t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>NATURASUL</t>
+          <t>NUTRIWEALTH</t>
         </is>
       </c>
       <c r="C1114" t="n">
@@ -28086,12 +28086,12 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>NTT</t>
+          <t>NUI</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>NATUPHITUS</t>
+          <t>NUTIVIT</t>
         </is>
       </c>
       <c r="C1115" t="n">
@@ -28111,12 +28111,12 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>NTU</t>
+          <t>NUL</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>NATURALIS</t>
+          <t>NUTRI LIFE SUPLEMENTOS ALIMENTARES E PRODUTOS NATURAIS</t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -28136,12 +28136,12 @@
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>NUB</t>
+          <t>NUM</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>NATUSBEL</t>
+          <t>NUTRI MIX</t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -28161,12 +28161,12 @@
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>NUC</t>
+          <t>NUN</t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>NUTRATEC</t>
+          <t>NUNATURE</t>
         </is>
       </c>
       <c r="C1118" t="n">
@@ -28186,12 +28186,12 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>NUD</t>
+          <t>NUO</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>NUTRI WIEDER</t>
+          <t>NUNO COSMETICOS</t>
         </is>
       </c>
       <c r="C1119" t="n">
@@ -28211,12 +28211,12 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>NUP</t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>NATUSER</t>
+          <t>NUTRIPLENO</t>
         </is>
       </c>
       <c r="C1120" t="n">
@@ -28236,12 +28236,12 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>NUF</t>
+          <t>NUR</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>NUTRAFOR</t>
+          <t>NUTRAFOL</t>
         </is>
       </c>
       <c r="C1121" t="n">
@@ -28261,12 +28261,12 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>NUG</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>NUTRIGEN</t>
+          <t>NATUS FARMA</t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -28286,12 +28286,12 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>NUH</t>
+          <t>NUT</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>NUTRIWEALTH</t>
+          <t>INDUSTRIA NUTRILAR</t>
         </is>
       </c>
       <c r="C1123" t="n">
@@ -28311,12 +28311,12 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>NUI</t>
+          <t>NUU</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>NUTIVIT</t>
+          <t>NATURE DO BRASIL</t>
         </is>
       </c>
       <c r="C1124" t="n">
@@ -28336,12 +28336,12 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>NUL</t>
+          <t>NUV</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>NUTRI LIFE SUPLEMENTOS ALIMENTARES E PRODUTOS NATURAIS</t>
+          <t>NUTRAVITTA</t>
         </is>
       </c>
       <c r="C1125" t="n">
@@ -28361,12 +28361,12 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>NUM</t>
+          <t>NUW</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>NUTRI MIX</t>
+          <t>NUTRAWAY</t>
         </is>
       </c>
       <c r="C1126" t="n">
@@ -28386,12 +28386,12 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>NUN</t>
+          <t>NUY</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>NUNATURE</t>
+          <t>NUTRI VITALEY</t>
         </is>
       </c>
       <c r="C1127" t="n">
@@ -28411,12 +28411,12 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>NUO</t>
+          <t>OCA</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>NUNO COSMETICOS</t>
+          <t>OCEANE</t>
         </is>
       </c>
       <c r="C1128" t="n">
@@ -28436,12 +28436,12 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>NUP</t>
+          <t>OIT</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>NUTRIPLENO</t>
+          <t>OITO ERVAS</t>
         </is>
       </c>
       <c r="C1129" t="n">
@@ -28461,12 +28461,12 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>NUR</t>
+          <t>OLD</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>NUTRAFOL</t>
+          <t>OLDVITTA</t>
         </is>
       </c>
       <c r="C1130" t="n">
@@ -28486,12 +28486,12 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>OME</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>NATUS FARMA</t>
+          <t>OMEGA</t>
         </is>
       </c>
       <c r="C1131" t="n">
@@ -28511,12 +28511,12 @@
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>NUT</t>
+          <t>OMI</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>INDUSTRIA NUTRILAR</t>
+          <t>OMIX</t>
         </is>
       </c>
       <c r="C1132" t="n">
@@ -28536,12 +28536,12 @@
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>NUU</t>
+          <t>OPH</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>NATURE DO BRASIL</t>
+          <t>OPHTHALMOS</t>
         </is>
       </c>
       <c r="C1133" t="n">
@@ -28561,12 +28561,12 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>NUV</t>
+          <t>OPI</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>NUTRAVITTA</t>
+          <t>OPTIMSM</t>
         </is>
       </c>
       <c r="C1134" t="n">
@@ -28586,12 +28586,12 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>NUW</t>
+          <t>OPM</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>NUTRAWAY</t>
+          <t>OPTIMUM NUTRITION</t>
         </is>
       </c>
       <c r="C1135" t="n">
@@ -28611,12 +28611,12 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>NUY</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>NUTRI VITALEY</t>
+          <t>OPTI SWISS</t>
         </is>
       </c>
       <c r="C1136" t="n">
@@ -28636,12 +28636,12 @@
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>OCA</t>
+          <t>ORA</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>OCEANE</t>
+          <t>ORANGE HEALTH</t>
         </is>
       </c>
       <c r="C1137" t="n">
@@ -28661,12 +28661,12 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>OIT</t>
+          <t>ORI</t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>OITO ERVAS</t>
+          <t>INDUSTRIA ORIENTAL LTDA</t>
         </is>
       </c>
       <c r="C1138" t="n">
@@ -28686,12 +28686,12 @@
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>OLD</t>
+          <t>ORT</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>OLDVITTA</t>
+          <t>ORTHO PAUHER</t>
         </is>
       </c>
       <c r="C1139" t="n">
@@ -28711,12 +28711,12 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>OME</t>
+          <t>OUE</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>OMEGA</t>
+          <t>OUREMMEL</t>
         </is>
       </c>
       <c r="C1140" t="n">
@@ -28736,12 +28736,12 @@
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>OMI</t>
+          <t>OUF</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>OMIX</t>
+          <t>OUROFINO</t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -28761,12 +28761,12 @@
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>OPH</t>
+          <t>OUO</t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>OPHTHALMOS</t>
+          <t>OUROCAPS INDUSTRIA DE PRODUTOS NATURAIS LTDA</t>
         </is>
       </c>
       <c r="C1142" t="n">
@@ -28786,12 +28786,12 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>OPI</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>OPTIMSM</t>
+          <t>OUTRA MARCA</t>
         </is>
       </c>
       <c r="C1143" t="n">
@@ -28811,12 +28811,12 @@
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>OPTIMUM NUTRITION</t>
+          <t>LABORATORIO PRADO</t>
         </is>
       </c>
       <c r="C1144" t="n">
@@ -28836,12 +28836,12 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>OPT</t>
+          <t>PAI</t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>OPTI SWISS</t>
+          <t>PAIXAO PRODUTOS FARMACEUTICOS</t>
         </is>
       </c>
       <c r="C1145" t="n">
@@ -28861,12 +28861,12 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>ORA</t>
+          <t>PAJ</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>ORANGE HEALTH</t>
+          <t>PAJE ALIMENTOS</t>
         </is>
       </c>
       <c r="C1146" t="n">
@@ -28886,12 +28886,12 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>ORI</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>INDUSTRIA ORIENTAL LTDA</t>
+          <t>PANTOVIN</t>
         </is>
       </c>
       <c r="C1147" t="n">
@@ -28911,12 +28911,12 @@
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>ORT</t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>ORTHO PAUHER</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="C1148" t="n">
@@ -28936,12 +28936,12 @@
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>OUE</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>OUREMMEL</t>
+          <t>PEAKNUTRI</t>
         </is>
       </c>
       <c r="C1149" t="n">
@@ -28961,12 +28961,12 @@
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>OUF</t>
+          <t>PEI</t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>OUROFINO</t>
+          <t>PEIXE ALIMENTOS</t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -28986,12 +28986,12 @@
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>OUO</t>
+          <t>PEM</t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>OUROCAPS INDUSTRIA DE PRODUTOS NATURAIS LTDA</t>
+          <t>PERMANENTE</t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -29011,12 +29011,12 @@
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>PEO</t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>OUTRA MARCA</t>
+          <t>PEIXOTO COM E IND</t>
         </is>
       </c>
       <c r="C1152" t="n">
@@ -29036,12 +29036,12 @@
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>PES</t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>LABORATORIO PRADO</t>
+          <t>PENSE FARMA</t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -29061,12 +29061,12 @@
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>PAI</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>PAIXAO PRODUTOS FARMACEUTICOS</t>
+          <t>GRUPO PETROPOLIS</t>
         </is>
       </c>
       <c r="C1154" t="n">
@@ -29086,12 +29086,12 @@
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>PAJ</t>
+          <t>PEX</t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>PAJE ALIMENTOS</t>
+          <t>PEIXINHO</t>
         </is>
       </c>
       <c r="C1155" t="n">
@@ -29111,12 +29111,12 @@
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>PFO</t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>PANTOVIN</t>
+          <t>PROFIT LABORATORIOS</t>
         </is>
       </c>
       <c r="C1156" t="n">
@@ -29136,12 +29136,12 @@
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>PAV</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PHD DO BRASIL</t>
         </is>
       </c>
       <c r="C1157" t="n">
@@ -29161,12 +29161,12 @@
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>PEAKNUTRI</t>
+          <t>PHITOMEL</t>
         </is>
       </c>
       <c r="C1158" t="n">
@@ -29186,12 +29186,12 @@
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>PEI</t>
+          <t>PHR</t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>PEIXE ALIMENTOS</t>
+          <t>PHARMAKOS D AMAZONIA</t>
         </is>
       </c>
       <c r="C1159" t="n">
@@ -29211,12 +29211,12 @@
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>PEM</t>
+          <t>PHT</t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>PERMANENTE</t>
+          <t>PHYTOVIVER</t>
         </is>
       </c>
       <c r="C1160" t="n">
@@ -29236,12 +29236,12 @@
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>PEO</t>
+          <t>PHY</t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>PEIXOTO COM E IND</t>
+          <t>PHYTONATUS</t>
         </is>
       </c>
       <c r="C1161" t="n">
@@ -29261,12 +29261,12 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>PIA</t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>PENSE FARMA</t>
+          <t>PIAVE COSMETICS</t>
         </is>
       </c>
       <c r="C1162" t="n">
@@ -29286,12 +29286,12 @@
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>GRUPO PETROPOLIS</t>
+          <t>PIERRY WERMAN</t>
         </is>
       </c>
       <c r="C1163" t="n">
@@ -29311,12 +29311,12 @@
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>PEX</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>PEIXINHO</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C1164" t="n">
@@ -29336,12 +29336,12 @@
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>PFO</t>
+          <t>PIJ</t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>PROFIT LABORATORIOS</t>
+          <t>PIJAMA DK</t>
         </is>
       </c>
       <c r="C1165" t="n">
@@ -29361,12 +29361,12 @@
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>PHD</t>
+          <t>PIM</t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>PHD DO BRASIL</t>
+          <t>PIMEL</t>
         </is>
       </c>
       <c r="C1166" t="n">
@@ -29386,12 +29386,12 @@
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>PHITOMEL</t>
+          <t>PINT PHARMA</t>
         </is>
       </c>
       <c r="C1167" t="n">
@@ -29411,12 +29411,12 @@
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>PHR</t>
+          <t>PLA</t>
         </is>
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>PHARMAKOS D AMAZONIA</t>
+          <t>PLANCTON</t>
         </is>
       </c>
       <c r="C1168" t="n">
@@ -29436,12 +29436,12 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>PHT</t>
+          <t>PLU</t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>PHYTOVIVER</t>
+          <t>PLURIX</t>
         </is>
       </c>
       <c r="C1169" t="n">
@@ -29461,12 +29461,12 @@
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>PHY</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>PHYTONATUS</t>
+          <t>PROMOFARMA</t>
         </is>
       </c>
       <c r="C1170" t="n">
@@ -29486,12 +29486,12 @@
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>PIA</t>
+          <t>POE</t>
         </is>
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>PIAVE COSMETICS</t>
+          <t>POWER SUPPLEMENTS</t>
         </is>
       </c>
       <c r="C1171" t="n">
@@ -29511,12 +29511,12 @@
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>POI</t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>PIERRY WERMAN</t>
+          <t>POLISTAR</t>
         </is>
       </c>
       <c r="C1172" t="n">
@@ -29536,12 +29536,12 @@
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>PII</t>
+          <t>POO</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>PRIME</t>
+          <t>PONTO DAS ERVAS</t>
         </is>
       </c>
       <c r="C1173" t="n">
@@ -29561,12 +29561,12 @@
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>PIJ</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>PIJAMA DK</t>
+          <t>POP MAX</t>
         </is>
       </c>
       <c r="C1174" t="n">
@@ -29586,12 +29586,12 @@
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>PIM</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>PIMEL</t>
+          <t>POSITIVE COMPANY</t>
         </is>
       </c>
       <c r="C1175" t="n">
@@ -29611,12 +29611,12 @@
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>POT</t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>PINT PHARMA</t>
+          <t>FARMA PONTE</t>
         </is>
       </c>
       <c r="C1176" t="n">
@@ -29636,12 +29636,12 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>PLA</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>PLANCTON</t>
+          <t>POWER GREEN</t>
         </is>
       </c>
       <c r="C1177" t="n">
@@ -29661,12 +29661,12 @@
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>PLU</t>
+          <t>POY</t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>PLURIX</t>
+          <t>POLYMARCAS GROUP</t>
         </is>
       </c>
       <c r="C1178" t="n">
@@ -29686,12 +29686,12 @@
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>PPM</t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>PROMOFARMA</t>
+          <t>PPM NUTRA</t>
         </is>
       </c>
       <c r="C1179" t="n">
@@ -29711,12 +29711,12 @@
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>POE</t>
+          <t>PRB</t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>POWER SUPPLEMENTS</t>
+          <t>PROBELLE COSMETICOS</t>
         </is>
       </c>
       <c r="C1180" t="n">
@@ -29736,12 +29736,12 @@
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>POI</t>
+          <t>PRC</t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>POLISTAR</t>
+          <t>PROPHARMACOS</t>
         </is>
       </c>
       <c r="C1181" t="n">
@@ -29761,12 +29761,12 @@
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>POO</t>
+          <t>PRH</t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>PONTO DAS ERVAS</t>
+          <t>PROHALL COSMETIC</t>
         </is>
       </c>
       <c r="C1182" t="n">
@@ -29786,12 +29786,12 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>PRI</t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>POP MAX</t>
+          <t>PRATIC LEVE</t>
         </is>
       </c>
       <c r="C1183" t="n">
@@ -29811,12 +29811,12 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>PRL</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>POSITIVE COMPANY</t>
+          <t>PROPOMEL PRODUTOS ALIMENTICIOS LTDA</t>
         </is>
       </c>
       <c r="C1184" t="n">
@@ -29836,12 +29836,12 @@
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>POT</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>FARMA PONTE</t>
+          <t>PREMIATTA</t>
         </is>
       </c>
       <c r="C1185" t="n">
@@ -29861,12 +29861,12 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>PRR</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>POWER GREEN</t>
+          <t>PRO ERVAS</t>
         </is>
       </c>
       <c r="C1186" t="n">
@@ -29886,12 +29886,12 @@
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>POY</t>
+          <t>PRS</t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>POLYMARCAS GROUP</t>
+          <t>PROFUSE</t>
         </is>
       </c>
       <c r="C1187" t="n">
@@ -29911,12 +29911,12 @@
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>PPM</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>PPM NUTRA</t>
+          <t>PRATIC</t>
         </is>
       </c>
       <c r="C1188" t="n">
@@ -29936,12 +29936,12 @@
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>PRB</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>PROBELLE COSMETICOS</t>
+          <t>PRODUTOS PRIMAVERA</t>
         </is>
       </c>
       <c r="C1189" t="n">
@@ -29961,12 +29961,12 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>PRC</t>
+          <t>PRV</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>PROPHARMACOS</t>
+          <t>PROVETS</t>
         </is>
       </c>
       <c r="C1190" t="n">
@@ -29986,12 +29986,12 @@
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>PRH</t>
+          <t>PRW</t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>PROHALL COSMETIC</t>
+          <t>PROWIN PHARMA</t>
         </is>
       </c>
       <c r="C1191" t="n">
@@ -30011,12 +30011,12 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>PRI</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>PRATIC LEVE</t>
+          <t>PRODAPYS</t>
         </is>
       </c>
       <c r="C1192" t="n">
@@ -30036,12 +30036,12 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>PRL</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>PROPOMEL PRODUTOS ALIMENTICIOS LTDA</t>
+          <t>PETRONAS</t>
         </is>
       </c>
       <c r="C1193" t="n">
@@ -30061,12 +30061,12 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>PUA</t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>PREMIATTA</t>
+          <t>PURAFOR</t>
         </is>
       </c>
       <c r="C1194" t="n">
@@ -30086,12 +30086,12 @@
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>PRR</t>
+          <t>QMA</t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>PRO ERVAS</t>
+          <t>Q MAIS VITTA</t>
         </is>
       </c>
       <c r="C1195" t="n">
@@ -30111,12 +30111,12 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>PRS</t>
+          <t>QUL</t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>PROFUSE</t>
+          <t>QUALYGRAOS DISTRIB ALIM</t>
         </is>
       </c>
       <c r="C1196" t="n">
@@ -30136,12 +30136,12 @@
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>RAD</t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>PRATIC</t>
+          <t>RADAR</t>
         </is>
       </c>
       <c r="C1197" t="n">
@@ -30161,12 +30161,12 @@
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>REA</t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>PRODUTOS PRIMAVERA</t>
+          <t>REAL H</t>
         </is>
       </c>
       <c r="C1198" t="n">
@@ -30186,12 +30186,12 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>PRV</t>
+          <t>REC</t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>PROVETS</t>
+          <t>RECORDATI</t>
         </is>
       </c>
       <c r="C1199" t="n">
@@ -30211,12 +30211,12 @@
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>PRW</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>PROWIN PHARMA</t>
+          <t>REDE ECONOMIZE</t>
         </is>
       </c>
       <c r="C1200" t="n">
@@ -30236,12 +30236,12 @@
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>REE</t>
         </is>
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>PRODAPYS</t>
+          <t>REDE KRILL</t>
         </is>
       </c>
       <c r="C1201" t="n">
@@ -30261,12 +30261,12 @@
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>PETRONAS</t>
+          <t>REFORM</t>
         </is>
       </c>
       <c r="C1202" t="n">
@@ -30286,12 +30286,12 @@
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>PUA</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>PURAFOR</t>
+          <t>REGINALDO ALVES DE LIMA</t>
         </is>
       </c>
       <c r="C1203" t="n">
@@ -30311,12 +30311,12 @@
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>QMA</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Q MAIS VITTA</t>
+          <t>REI DOS CONDIMENTOS</t>
         </is>
       </c>
       <c r="C1204" t="n">
@@ -30336,12 +30336,12 @@
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>QUL</t>
+          <t>REL</t>
         </is>
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>QUALYGRAOS DISTRIB ALIM</t>
+          <t>REDE MELHOR COMPRA</t>
         </is>
       </c>
       <c r="C1205" t="n">
@@ -30361,12 +30361,12 @@
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>RAD</t>
+          <t>REM</t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>RADAR</t>
+          <t>REDE MASTERFARMA</t>
         </is>
       </c>
       <c r="C1206" t="n">
@@ -30386,12 +30386,12 @@
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>REAL H</t>
+          <t>RENKS INDUSTRIAL</t>
         </is>
       </c>
       <c r="C1207" t="n">
@@ -30411,12 +30411,12 @@
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>REC</t>
+          <t>REO</t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>RECORDATI</t>
+          <t>REIDRAT IND E COM DE PROD ALIM LTDA</t>
         </is>
       </c>
       <c r="C1208" t="n">
@@ -30436,12 +30436,12 @@
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>REP</t>
         </is>
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>REDE ECONOMIZE</t>
+          <t>REDE SP</t>
         </is>
       </c>
       <c r="C1209" t="n">
@@ -30461,12 +30461,12 @@
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>REE</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>REDE KRILL</t>
+          <t>REI TERRA</t>
         </is>
       </c>
       <c r="C1210" t="n">
@@ -30486,12 +30486,12 @@
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>REFORM</t>
+          <t>REDE SOMA DROGARIAS</t>
         </is>
       </c>
       <c r="C1211" t="n">
@@ -30511,12 +30511,12 @@
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>REU</t>
         </is>
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>REGINALDO ALVES DE LIMA</t>
+          <t>RELUZ COSMETICOS</t>
         </is>
       </c>
       <c r="C1212" t="n">
@@ -30536,12 +30536,12 @@
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>REW</t>
         </is>
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>REI DOS CONDIMENTOS</t>
+          <t>REVIEW CARE</t>
         </is>
       </c>
       <c r="C1213" t="n">
@@ -30561,12 +30561,12 @@
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>REL</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>REDE MELHOR COMPRA</t>
+          <t>RH COSMETICOS</t>
         </is>
       </c>
       <c r="C1214" t="n">
@@ -30586,12 +30586,12 @@
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>REM</t>
+          <t>RHE</t>
         </is>
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>REDE MASTERFARMA</t>
+          <t>RHENUKS</t>
         </is>
       </c>
       <c r="C1215" t="n">
@@ -30611,12 +30611,12 @@
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>RENKS INDUSTRIAL</t>
+          <t>RICHEE</t>
         </is>
       </c>
       <c r="C1216" t="n">
@@ -30636,12 +30636,12 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>REO</t>
+          <t>RIL</t>
         </is>
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>REIDRAT IND E COM DE PROD ALIM LTDA</t>
+          <t>RICLAN</t>
         </is>
       </c>
       <c r="C1217" t="n">
@@ -30661,12 +30661,12 @@
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>REP</t>
+          <t>RNN</t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>REDE SP</t>
+          <t>RENOVIT</t>
         </is>
       </c>
       <c r="C1218" t="n">
@@ -30686,12 +30686,12 @@
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>REI TERRA</t>
+          <t>RN SUPLEMENTOS</t>
         </is>
       </c>
       <c r="C1219" t="n">
@@ -30711,12 +30711,12 @@
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>ROA</t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>REDE SOMA DROGARIAS</t>
+          <t>ROCHADEL COM IND</t>
         </is>
       </c>
       <c r="C1220" t="n">
@@ -30736,12 +30736,12 @@
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>REU</t>
+          <t>ROH</t>
         </is>
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>RELUZ COSMETICOS</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="C1221" t="n">
@@ -30761,12 +30761,12 @@
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>REW</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>REVIEW CARE</t>
+          <t>ROKEE PROFESSIONAL</t>
         </is>
       </c>
       <c r="C1222" t="n">
@@ -30786,12 +30786,12 @@
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>ROM</t>
         </is>
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>RH COSMETICOS</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C1223" t="n">
@@ -30811,12 +30811,12 @@
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>RHE</t>
+          <t>ROS</t>
         </is>
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>RHENUKS</t>
+          <t>ROSA RAIZ</t>
         </is>
       </c>
       <c r="C1224" t="n">
@@ -30836,12 +30836,12 @@
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>RPP</t>
         </is>
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>RICHEE</t>
+          <t>REPOS</t>
         </is>
       </c>
       <c r="C1225" t="n">
@@ -30861,12 +30861,12 @@
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>RIL</t>
+          <t>RTK</t>
         </is>
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>RICLAN</t>
+          <t>RTK COS E ALIM NATURAIS</t>
         </is>
       </c>
       <c r="C1226" t="n">
@@ -30886,12 +30886,12 @@
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>RVV</t>
         </is>
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>RIOQUIMICA</t>
+          <t>REVIVARE</t>
         </is>
       </c>
       <c r="C1227" t="n">
@@ -30911,12 +30911,12 @@
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>RNN</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>RENOVIT</t>
+          <t>SAN MAR</t>
         </is>
       </c>
       <c r="C1228" t="n">
@@ -30936,12 +30936,12 @@
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>RN SUPLEMENTOS</t>
+          <t>SABOR DA SERRA CIA</t>
         </is>
       </c>
       <c r="C1229" t="n">
@@ -30961,12 +30961,12 @@
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>ROA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>ROCHADEL COM IND</t>
+          <t>SANTANA IMPORTACAO E EXPORTACAO</t>
         </is>
       </c>
       <c r="C1230" t="n">
@@ -30986,12 +30986,12 @@
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>ROH</t>
+          <t>SAD</t>
         </is>
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>SAUDE IND</t>
         </is>
       </c>
       <c r="C1231" t="n">
@@ -31011,12 +31011,12 @@
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>SAE</t>
         </is>
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>ROKEE PROFESSIONAL</t>
+          <t>SAO CAETANO</t>
         </is>
       </c>
       <c r="C1232" t="n">
@@ -31036,12 +31036,12 @@
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>ROM</t>
+          <t>SAF</t>
         </is>
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SANFARMA LTDA</t>
         </is>
       </c>
       <c r="C1233" t="n">
@@ -31061,12 +31061,12 @@
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>ROS</t>
+          <t>SAJ</t>
         </is>
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>ROSA RAIZ</t>
+          <t>SAN JULLY COSMETICOS</t>
         </is>
       </c>
       <c r="C1234" t="n">
@@ -31086,12 +31086,12 @@
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>RPP</t>
+          <t>SAL</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>REPOS</t>
+          <t>SALVATORE</t>
         </is>
       </c>
       <c r="C1235" t="n">
@@ -31111,12 +31111,12 @@
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>RTK</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>RTK COS E ALIM NATURAIS</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="C1236" t="n">
@@ -31136,12 +31136,12 @@
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>RVV</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>REVIVARE</t>
+          <t>SAN PRIME IND E DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="C1237" t="n">
@@ -31161,12 +31161,12 @@
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>SAN MAR</t>
+          <t>SAO JOAQUIM CAFE</t>
         </is>
       </c>
       <c r="C1238" t="n">
@@ -31186,12 +31186,12 @@
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>SABOR DA SERRA CIA</t>
+          <t>SABORELLE CIA</t>
         </is>
       </c>
       <c r="C1239" t="n">
@@ -31211,12 +31211,12 @@
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>SANTANA IMPORTACAO E EXPORTACAO</t>
+          <t>SANIBRAS MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C1240" t="n">
@@ -31236,12 +31236,12 @@
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>SAD</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>SAUDE IND</t>
+          <t>LABORATORIO SAUDE</t>
         </is>
       </c>
       <c r="C1241" t="n">
@@ -31261,12 +31261,12 @@
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>SAE</t>
+          <t>SAV</t>
         </is>
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>SAO CAETANO</t>
+          <t>SANAVITA</t>
         </is>
       </c>
       <c r="C1242" t="n">
@@ -31286,12 +31286,12 @@
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>SAF</t>
+          <t>SAY</t>
         </is>
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>SANFARMA LTDA</t>
+          <t>SATYA</t>
         </is>
       </c>
       <c r="C1243" t="n">
@@ -31311,12 +31311,12 @@
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>SAJ</t>
+          <t>SAZ</t>
         </is>
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>SAN JULLY COSMETICOS</t>
+          <t>SAO RAIZEIRO</t>
         </is>
       </c>
       <c r="C1244" t="n">
@@ -31336,12 +31336,12 @@
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>SAL</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>SALVATORE</t>
+          <t>SNC</t>
         </is>
       </c>
       <c r="C1245" t="n">
@@ -31361,12 +31361,12 @@
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>SCE</t>
         </is>
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>SCELTI</t>
         </is>
       </c>
       <c r="C1246" t="n">
@@ -31386,12 +31386,12 @@
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>SAN PRIME IND E DISTRIBUIDORA LTDA</t>
+          <t>SCHILLIFE IND E COM LTDA</t>
         </is>
       </c>
       <c r="C1247" t="n">
@@ -31411,12 +31411,12 @@
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SCU</t>
         </is>
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>SAO JOAQUIM CAFE</t>
+          <t>SCHUCK</t>
         </is>
       </c>
       <c r="C1248" t="n">
@@ -31436,12 +31436,12 @@
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>SABORELLE CIA</t>
+          <t>SEMPREBOM</t>
         </is>
       </c>
       <c r="C1249" t="n">
@@ -31461,12 +31461,12 @@
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>SANIBRAS MEDICAMENTOS</t>
+          <t>SERGIO PARIS</t>
         </is>
       </c>
       <c r="C1250" t="n">
@@ -31486,12 +31486,12 @@
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>LABORATORIO SAUDE</t>
+          <t>SELECT NUTRI</t>
         </is>
       </c>
       <c r="C1251" t="n">
@@ -31511,12 +31511,12 @@
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>SAV</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>SANAVITA</t>
+          <t>SEMPRE</t>
         </is>
       </c>
       <c r="C1252" t="n">
@@ -31536,12 +31536,12 @@
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>SAY</t>
+          <t>SEV</t>
         </is>
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>SATYA</t>
+          <t>SETE ERVAS</t>
         </is>
       </c>
       <c r="C1253" t="n">
@@ -31561,12 +31561,12 @@
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>SAZ</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>SAO RAIZEIRO</t>
+          <t>SHAMBALA</t>
         </is>
       </c>
       <c r="C1254" t="n">
@@ -31586,12 +31586,12 @@
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>SHE</t>
         </is>
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>SNC</t>
+          <t>SHIRE</t>
         </is>
       </c>
       <c r="C1255" t="n">
@@ -31611,12 +31611,12 @@
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>SCE</t>
+          <t>SHI</t>
         </is>
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>SCELTI</t>
+          <t>SHINEBLUE COSM</t>
         </is>
       </c>
       <c r="C1256" t="n">
@@ -31636,12 +31636,12 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>SHM</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>SCHILLIFE IND E COM LTDA</t>
+          <t>SHAMBALA IND E COM DE PROD NATURAIS LTDA</t>
         </is>
       </c>
       <c r="C1257" t="n">
@@ -31661,12 +31661,12 @@
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>SCU</t>
+          <t>SHO</t>
         </is>
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>SCHUCK</t>
+          <t>SHOOPNATU</t>
         </is>
       </c>
       <c r="C1258" t="n">
@@ -31686,12 +31686,12 @@
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SHR</t>
         </is>
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>SEMPREBOM</t>
+          <t>SHARK PRO</t>
         </is>
       </c>
       <c r="C1259" t="n">
@@ -31711,12 +31711,12 @@
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SHT</t>
         </is>
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>SERGIO PARIS</t>
+          <t>SHOT ME</t>
         </is>
       </c>
       <c r="C1260" t="n">
@@ -31736,12 +31736,12 @@
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>SIA</t>
         </is>
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>SELECT NUTRI</t>
+          <t>SILVERNATUS</t>
         </is>
       </c>
       <c r="C1261" t="n">
@@ -31761,12 +31761,12 @@
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>SIE</t>
         </is>
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>SEMPRE</t>
+          <t>SIDNEY OLIVEIRA</t>
         </is>
       </c>
       <c r="C1262" t="n">
@@ -31786,12 +31786,12 @@
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>SETE ERVAS</t>
+          <t>SIGMA PHARMA</t>
         </is>
       </c>
       <c r="C1263" t="n">
@@ -31811,12 +31811,12 @@
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>SHAMBALA</t>
+          <t>SILLAGE</t>
         </is>
       </c>
       <c r="C1264" t="n">
@@ -31836,12 +31836,12 @@
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>SHE</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>SHIRE</t>
+          <t>SIMILASAN</t>
         </is>
       </c>
       <c r="C1265" t="n">
@@ -31861,12 +31861,12 @@
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>SHI</t>
+          <t>SIR</t>
         </is>
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>SHINEBLUE COSM</t>
+          <t>DE SIRIUS COSMETICOS</t>
         </is>
       </c>
       <c r="C1266" t="n">
@@ -31886,12 +31886,12 @@
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>SHM</t>
+          <t>SIS</t>
         </is>
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>SHAMBALA IND E COM DE PROD NATURAIS LTDA</t>
+          <t>SILVESTRE</t>
         </is>
       </c>
       <c r="C1267" t="n">
@@ -31911,12 +31911,12 @@
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>SHO</t>
+          <t>SIT</t>
         </is>
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>SHOOPNATU</t>
+          <t>SITIO PURA VIDA</t>
         </is>
       </c>
       <c r="C1268" t="n">
@@ -31936,12 +31936,12 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>SIV</t>
         </is>
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>SHARK PRO</t>
+          <t>SILVER NATUS</t>
         </is>
       </c>
       <c r="C1269" t="n">
@@ -31961,12 +31961,12 @@
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>SHT</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>SHOT ME</t>
+          <t>SKAFE</t>
         </is>
       </c>
       <c r="C1270" t="n">
@@ -31986,12 +31986,12 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>SIA</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>SILVERNATUS</t>
+          <t>SOLARIS PHARMA</t>
         </is>
       </c>
       <c r="C1271" t="n">
@@ -32011,12 +32011,12 @@
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>SIE</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>SIDNEY OLIVEIRA</t>
+          <t>SOLARIS IND E COM DE ALIM</t>
         </is>
       </c>
       <c r="C1272" t="n">
@@ -32036,12 +32036,12 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>SML</t>
         </is>
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>SIGMA PHARMA</t>
+          <t>SOMAR LIFE</t>
         </is>
       </c>
       <c r="C1273" t="n">
@@ -32061,12 +32061,12 @@
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SMM</t>
         </is>
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>SILLAGE</t>
+          <t>SEM</t>
         </is>
       </c>
       <c r="C1274" t="n">
@@ -32086,12 +32086,12 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>SIMILASAN</t>
+          <t>SMART COM DE ALIM LTDA</t>
         </is>
       </c>
       <c r="C1275" t="n">
@@ -32111,12 +32111,12 @@
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>SIR</t>
+          <t>SNN</t>
         </is>
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>DE SIRIUS COSMETICOS</t>
+          <t>SANOFI FARMACEUTICA LTDA</t>
         </is>
       </c>
       <c r="C1276" t="n">
@@ -32136,12 +32136,12 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>SIS</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>SILVESTRE</t>
+          <t>SOBRAL</t>
         </is>
       </c>
       <c r="C1277" t="n">
@@ -32161,12 +32161,12 @@
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>SIT</t>
+          <t>SOC</t>
         </is>
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>SITIO PURA VIDA</t>
+          <t>SOUL COSMETICOS</t>
         </is>
       </c>
       <c r="C1278" t="n">
@@ -32186,12 +32186,12 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>SIV</t>
+          <t>SOD</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>SILVER NATUS</t>
+          <t>SOLIDOR</t>
         </is>
       </c>
       <c r="C1279" t="n">
@@ -32211,12 +32211,12 @@
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOE</t>
         </is>
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>SKAFE</t>
+          <t>SOL BEBIDAS</t>
         </is>
       </c>
       <c r="C1280" t="n">
@@ -32236,12 +32236,12 @@
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>SOF</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>SOLARIS PHARMA</t>
+          <t>SOMALIFE</t>
         </is>
       </c>
       <c r="C1281" t="n">
@@ -32261,12 +32261,12 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>SOI</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>SOLARIS IND E COM DE ALIM</t>
+          <t>SOL BEBIDAS LTDA</t>
         </is>
       </c>
       <c r="C1282" t="n">
@@ -32286,12 +32286,12 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>SML</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>SOMAR LIFE</t>
+          <t>SO MEL</t>
         </is>
       </c>
       <c r="C1283" t="n">
@@ -32311,12 +32311,12 @@
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>SMM</t>
+          <t>SOO</t>
         </is>
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>SEM</t>
+          <t>SAO CARLOS</t>
         </is>
       </c>
       <c r="C1284" t="n">
@@ -32336,12 +32336,12 @@
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>SOV</t>
         </is>
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>SMART COM DE ALIM LTDA</t>
+          <t>SOLVAY FARMA</t>
         </is>
       </c>
       <c r="C1285" t="n">
@@ -32361,12 +32361,12 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>SNN</t>
+          <t>SOY</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>SANOFI FARMACEUTICA LTDA</t>
+          <t>SOULY</t>
         </is>
       </c>
       <c r="C1286" t="n">
@@ -32386,12 +32386,12 @@
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SPE</t>
         </is>
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>SOBRAL</t>
+          <t>SUPRAERVAS</t>
         </is>
       </c>
       <c r="C1287" t="n">
@@ -32411,12 +32411,12 @@
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>SOUL COSMETICOS</t>
+          <t>SPIRRO</t>
         </is>
       </c>
       <c r="C1288" t="n">
@@ -32436,12 +32436,12 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>SOD</t>
+          <t>SPP</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>SOLIDOR</t>
+          <t>SUPERMEL</t>
         </is>
       </c>
       <c r="C1289" t="n">
@@ -32461,12 +32461,12 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>SOE</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>SOL BEBIDAS</t>
+          <t>STARFARMA</t>
         </is>
       </c>
       <c r="C1290" t="n">
@@ -32486,12 +32486,12 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>SOF</t>
+          <t>STF</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>SOMALIFE</t>
+          <t>STEFFENON ALIMENTOS</t>
         </is>
       </c>
       <c r="C1291" t="n">
@@ -32511,12 +32511,12 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>SOI</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>SOL BEBIDAS LTDA</t>
+          <t>STARTFARMA</t>
         </is>
       </c>
       <c r="C1292" t="n">
@@ -32536,12 +32536,12 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>STY</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>SO MEL</t>
+          <t>STYLOFARMA</t>
         </is>
       </c>
       <c r="C1293" t="n">
@@ -32561,12 +32561,12 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>SOO</t>
+          <t>SUA</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>SAO CARLOS</t>
+          <t>SUAV NUTRITION</t>
         </is>
       </c>
       <c r="C1294" t="n">
@@ -32586,12 +32586,12 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>SOV</t>
+          <t>SUB</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>SOLVAY FARMA</t>
+          <t>SUPRA ERVAS BEBIDAS</t>
         </is>
       </c>
       <c r="C1295" t="n">
@@ -32611,12 +32611,12 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>SOY</t>
+          <t>SUE</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>SOULY</t>
+          <t>SUPER REDE</t>
         </is>
       </c>
       <c r="C1296" t="n">
@@ -32636,12 +32636,12 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>SUF</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>SUPRAERVAS</t>
+          <t>SUNFLOWER</t>
         </is>
       </c>
       <c r="C1297" t="n">
@@ -32661,12 +32661,12 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>SPIRRO</t>
+          <t>GRUPO SUISSA</t>
         </is>
       </c>
       <c r="C1298" t="n">
@@ -32686,12 +32686,12 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>SPP</t>
+          <t>SUL</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>SUPERMEL</t>
+          <t>SULMEL</t>
         </is>
       </c>
       <c r="C1299" t="n">
@@ -32711,12 +32711,12 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>STARFARMA</t>
+          <t>SUMITOMO CHEMICAL BRASIL</t>
         </is>
       </c>
       <c r="C1300" t="n">
@@ -32736,12 +32736,12 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>STF</t>
+          <t>SUP</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>STEFFENON ALIMENTOS</t>
+          <t>SUPER HEALTH</t>
         </is>
       </c>
       <c r="C1301" t="n">
@@ -32761,12 +32761,12 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>STARTFARMA</t>
+          <t>SUPERIORE INDUSTRIA DE PRODUTOS ALIMENTICIOS</t>
         </is>
       </c>
       <c r="C1302" t="n">
@@ -32786,12 +32786,12 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>STY</t>
+          <t>SUT</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>STYLOFARMA</t>
+          <t>SUPRA ALIMENTOS</t>
         </is>
       </c>
       <c r="C1303" t="n">
@@ -32811,12 +32811,12 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>SUA</t>
+          <t>SUU</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>SUAV NUTRITION</t>
+          <t>SOUL BRASIL</t>
         </is>
       </c>
       <c r="C1304" t="n">
@@ -32836,12 +32836,12 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>SUB</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>SUPRA ERVAS BEBIDAS</t>
+          <t>SUPERVITAN</t>
         </is>
       </c>
       <c r="C1305" t="n">
@@ -32861,12 +32861,12 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>SUE</t>
+          <t>SUX</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>SUPER REDE</t>
+          <t>SUPERMAX BRASIL</t>
         </is>
       </c>
       <c r="C1306" t="n">
@@ -32886,12 +32886,12 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>SUF</t>
+          <t>SUY</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>SUNFLOWER</t>
+          <t>SUPLEY</t>
         </is>
       </c>
       <c r="C1307" t="n">
@@ -32911,12 +32911,12 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>SWA</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>GRUPO SUISSA</t>
+          <t>SWANSON</t>
         </is>
       </c>
       <c r="C1308" t="n">
@@ -32936,12 +32936,12 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>SUL</t>
+          <t>TAP</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>SULMEL</t>
+          <t>GRUPO TAPAJOS</t>
         </is>
       </c>
       <c r="C1309" t="n">
@@ -32961,12 +32961,12 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>TAU</t>
         </is>
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>SUMITOMO CHEMICAL BRASIL</t>
+          <t>TAUENS</t>
         </is>
       </c>
       <c r="C1310" t="n">
@@ -32986,12 +32986,12 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>SUP</t>
+          <t>TCM</t>
         </is>
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>SUPER HEALTH</t>
+          <t>TCM</t>
         </is>
       </c>
       <c r="C1311" t="n">
@@ -33011,12 +33011,12 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>TEA</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>SUPERIORE INDUSTRIA DE PRODUTOS ALIMENTICIOS</t>
+          <t>TERRA MAIS</t>
         </is>
       </c>
       <c r="C1312" t="n">
@@ -33036,12 +33036,12 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>SUT</t>
+          <t>TEC</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>SUPRA ALIMENTOS</t>
+          <t>TEC SNACKS</t>
         </is>
       </c>
       <c r="C1313" t="n">
@@ -33061,12 +33061,12 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>SUU</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>SOUL BRASIL</t>
+          <t>TERRA E SAUDE</t>
         </is>
       </c>
       <c r="C1314" t="n">
@@ -33086,12 +33086,12 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>SUV</t>
+          <t>TES</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>SUPERVITAN</t>
+          <t>TERRA SANTA ALIMENTOS</t>
         </is>
       </c>
       <c r="C1315" t="n">
@@ -33111,12 +33111,12 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>SUX</t>
+          <t>THL</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>SUPERMAX BRASIL</t>
+          <t>THREE LIFE</t>
         </is>
       </c>
       <c r="C1316" t="n">
@@ -33136,12 +33136,12 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>SUY</t>
+          <t>TIR</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>SUPLEY</t>
+          <t>TIARAJU</t>
         </is>
       </c>
       <c r="C1317" t="n">
@@ -33161,12 +33161,12 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>SWA</t>
+          <t>TOF</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>SWANSON</t>
+          <t>TOFF</t>
         </is>
       </c>
       <c r="C1318" t="n">
@@ -33186,12 +33186,12 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>TOK</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>GRUPO TAPAJOS</t>
+          <t>TOK BOTHANICO</t>
         </is>
       </c>
       <c r="C1319" t="n">
@@ -33211,12 +33211,12 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>TAU</t>
+          <t>TON</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>TAUENS</t>
+          <t>TOP NEW SUPLEMENTOS</t>
         </is>
       </c>
       <c r="C1320" t="n">
@@ -33236,12 +33236,12 @@
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>TCM</t>
+          <t>TOS</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>TCM</t>
+          <t>TOSHI</t>
         </is>
       </c>
       <c r="C1321" t="n">
@@ -33261,12 +33261,12 @@
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>TEA</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>TERRA MAIS</t>
+          <t>TOTAL QUIMICA</t>
         </is>
       </c>
       <c r="C1322" t="n">
@@ -33286,12 +33286,12 @@
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>TEC</t>
+          <t>TOW</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>TEC SNACKS</t>
+          <t>TOPWAY NUTRITION</t>
         </is>
       </c>
       <c r="C1323" t="n">
@@ -33311,12 +33311,12 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TRA</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>TERRA E SAUDE</t>
+          <t>TRATTA BRASIL</t>
         </is>
       </c>
       <c r="C1324" t="n">
@@ -33336,12 +33336,12 @@
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>TES</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>TERRA SANTA ALIMENTOS</t>
+          <t>TRISKLE COSM</t>
         </is>
       </c>
       <c r="C1325" t="n">
@@ -33361,12 +33361,12 @@
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>THL</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>THREE LIFE</t>
+          <t>TROPICAL CONDIMENTOS</t>
         </is>
       </c>
       <c r="C1326" t="n">
@@ -33386,12 +33386,12 @@
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>TIR</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>TIARAJU</t>
+          <t>TUTTI</t>
         </is>
       </c>
       <c r="C1327" t="n">
@@ -33411,12 +33411,12 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>UII</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>TOFF</t>
+          <t>UNILAR</t>
         </is>
       </c>
       <c r="C1328" t="n">
@@ -33436,12 +33436,12 @@
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>TOK</t>
+          <t>UNA</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>TOK BOTHANICO</t>
+          <t>UNIAO</t>
         </is>
       </c>
       <c r="C1329" t="n">
@@ -33461,12 +33461,12 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>TON</t>
+          <t>UNE</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>TOP NEW SUPLEMENTOS</t>
+          <t>UNDER LABZ</t>
         </is>
       </c>
       <c r="C1330" t="n">
@@ -33486,12 +33486,12 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>TOS</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>TOSHI</t>
+          <t>UNIMEL</t>
         </is>
       </c>
       <c r="C1331" t="n">
@@ -33511,12 +33511,12 @@
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>TOTAL QUIMICA</t>
+          <t>UNI NUTRE</t>
         </is>
       </c>
       <c r="C1332" t="n">
@@ -33536,12 +33536,12 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>TOW</t>
+          <t>UNR</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>TOPWAY NUTRITION</t>
+          <t>UNIAO FLORA</t>
         </is>
       </c>
       <c r="C1333" t="n">
@@ -33561,12 +33561,12 @@
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>TRA</t>
+          <t>UNT</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>TRATTA BRASIL</t>
+          <t>UNITHER BRASIL</t>
         </is>
       </c>
       <c r="C1334" t="n">
@@ -33586,12 +33586,12 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>UNV</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>TRISKLE COSM</t>
+          <t>UNILEVER</t>
         </is>
       </c>
       <c r="C1335" t="n">
@@ -33611,12 +33611,12 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>VAA</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>TROPICAL CONDIMENTOS</t>
+          <t>VITTALIFE</t>
         </is>
       </c>
       <c r="C1336" t="n">
@@ -33636,12 +33636,12 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>VAE</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>TUTTI</t>
+          <t>VALE DO MEL</t>
         </is>
       </c>
       <c r="C1337" t="n">
@@ -33661,12 +33661,12 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>UII</t>
+          <t>VAS</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>UNILAR</t>
+          <t>VASSOURAS DRAGAO</t>
         </is>
       </c>
       <c r="C1338" t="n">
@@ -33686,12 +33686,12 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>UNA</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>UNIAO</t>
+          <t>VITAVIT</t>
         </is>
       </c>
       <c r="C1339" t="n">
@@ -33711,12 +33711,12 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>UNE</t>
+          <t>VCA</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>UNDER LABZ</t>
+          <t>VCA</t>
         </is>
       </c>
       <c r="C1340" t="n">
@@ -33736,12 +33736,12 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>VEE</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>UNIMEL</t>
+          <t>VEGETAL LABS</t>
         </is>
       </c>
       <c r="C1341" t="n">
@@ -33761,12 +33761,12 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>UNI NUTRE</t>
+          <t>VENEZA HAIR COSM</t>
         </is>
       </c>
       <c r="C1342" t="n">
@@ -33786,12 +33786,12 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>UNR</t>
+          <t>VER</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>UNIAO FLORA</t>
+          <t>VERDEMED</t>
         </is>
       </c>
       <c r="C1343" t="n">
@@ -33811,12 +33811,12 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>UNT</t>
+          <t>VHI</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>UNITHER BRASIL</t>
+          <t>VHITA DISTRIBUIDORA DE VITAMINAS LTDA</t>
         </is>
       </c>
       <c r="C1344" t="n">
@@ -33836,12 +33836,12 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>UNV</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>UNILEVER</t>
+          <t>VILLAGE CEPAM</t>
         </is>
       </c>
       <c r="C1345" t="n">
@@ -33861,12 +33861,12 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>VAA</t>
+          <t>VID</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>VITTALIFE</t>
+          <t>VIDEIRA 7</t>
         </is>
       </c>
       <c r="C1346" t="n">
@@ -33886,12 +33886,12 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>VAE</t>
+          <t>VIE</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>VALE DO MEL</t>
+          <t>VIA TERRA PRODUTOS NATURAIS</t>
         </is>
       </c>
       <c r="C1347" t="n">
@@ -33911,12 +33911,12 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>VAS</t>
+          <t>VIF</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>VASSOURAS DRAGAO</t>
+          <t>VIDFARMA</t>
         </is>
       </c>
       <c r="C1348" t="n">
@@ -33936,12 +33936,12 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>VIG</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>VITAVIT</t>
+          <t>VILLAGE</t>
         </is>
       </c>
       <c r="C1349" t="n">
@@ -33961,12 +33961,12 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>VCA</t>
+          <t>VII</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>VCA</t>
+          <t>VITA MEDICAL</t>
         </is>
       </c>
       <c r="C1350" t="n">
@@ -33986,12 +33986,12 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>VIL</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>VEGETAL LABS</t>
+          <t>GRUPO VILA ERVAS</t>
         </is>
       </c>
       <c r="C1351" t="n">
@@ -34011,12 +34011,12 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>VIM</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>VENEZA HAIR COSM</t>
+          <t>VITA DERM COSMETICA</t>
         </is>
       </c>
       <c r="C1352" t="n">
@@ -34036,12 +34036,12 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>VER</t>
+          <t>VIO</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>VERDEMED</t>
+          <t>VITA FLORA</t>
         </is>
       </c>
       <c r="C1353" t="n">
@@ -34061,12 +34061,12 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>VHI</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>VHITA DISTRIBUIDORA DE VITAMINAS LTDA</t>
+          <t>VITALCORP</t>
         </is>
       </c>
       <c r="C1354" t="n">
@@ -34086,12 +34086,12 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>VIR</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>VILLAGE CEPAM</t>
+          <t>VILA ERVAS</t>
         </is>
       </c>
       <c r="C1355" t="n">
@@ -34111,12 +34111,12 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>VID</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>VIDEIRA 7</t>
+          <t>FARMA VISION</t>
         </is>
       </c>
       <c r="C1356" t="n">
@@ -34136,12 +34136,12 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>VIE</t>
+          <t>VIU</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>VIA TERRA PRODUTOS NATURAIS</t>
+          <t>VITAGENUS</t>
         </is>
       </c>
       <c r="C1357" t="n">
@@ -34161,12 +34161,12 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>VIF</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>VIDFARMA</t>
+          <t>VITA VITA COM IND EXP IMP LTDA</t>
         </is>
       </c>
       <c r="C1358" t="n">
@@ -34186,12 +34186,12 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>VIG</t>
+          <t>VIZ</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>VILLAGE</t>
+          <t>VIZET</t>
         </is>
       </c>
       <c r="C1359" t="n">
@@ -34211,12 +34211,12 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>VLL</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>VITA MEDICAL</t>
+          <t>VILAVET</t>
         </is>
       </c>
       <c r="C1360" t="n">
@@ -34236,12 +34236,12 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>VIL</t>
+          <t>VOG</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>GRUPO VILA ERVAS</t>
+          <t>VOGHIERA</t>
         </is>
       </c>
       <c r="C1361" t="n">
@@ -34261,12 +34261,12 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>VIM</t>
+          <t>VOV</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>VITA DERM COSMETICA</t>
+          <t>VOVO ISABEL</t>
         </is>
       </c>
       <c r="C1362" t="n">
@@ -34286,12 +34286,12 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>VIO</t>
+          <t>VTA</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>VITA FLORA</t>
+          <t>VITA</t>
         </is>
       </c>
       <c r="C1363" t="n">
@@ -34311,12 +34311,12 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>VTC</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>VITALCORP</t>
+          <t>VITTA CARE</t>
         </is>
       </c>
       <c r="C1364" t="n">
@@ -34336,12 +34336,12 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>VILA ERVAS</t>
+          <t>VITERNAT</t>
         </is>
       </c>
       <c r="C1365" t="n">
@@ -34361,12 +34361,12 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>FARMA VISION</t>
+          <t>VITAMINAS RACOES</t>
         </is>
       </c>
       <c r="C1366" t="n">
@@ -34386,12 +34386,12 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>VIU</t>
+          <t>VTO</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>VITAGENUS</t>
+          <t>VITTORE</t>
         </is>
       </c>
       <c r="C1367" t="n">
@@ -34411,12 +34411,12 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>VTT</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>VITA VITA COM IND EXP IMP LTDA</t>
+          <t>VIT</t>
         </is>
       </c>
       <c r="C1368" t="n">
@@ -34436,12 +34436,12 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>VIZ</t>
+          <t>VTV</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>VIZET</t>
+          <t>VITAVANT</t>
         </is>
       </c>
       <c r="C1369" t="n">
@@ -34461,12 +34461,12 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>VLL</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>VILAVET</t>
+          <t>VITAMAX NUTRITION</t>
         </is>
       </c>
       <c r="C1370" t="n">
@@ -34486,12 +34486,12 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>VOG</t>
+          <t>VVA</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>VOGHIERA</t>
+          <t>VIVAI COSMETICOS</t>
         </is>
       </c>
       <c r="C1371" t="n">
@@ -34511,12 +34511,12 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>VOV</t>
+          <t>VVI</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>VOVO ISABEL</t>
+          <t>VIVAMIL</t>
         </is>
       </c>
       <c r="C1372" t="n">
@@ -34536,12 +34536,12 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>VTA</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>VITA</t>
+          <t>VIVA REGENERA</t>
         </is>
       </c>
       <c r="C1373" t="n">
@@ -34561,12 +34561,12 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>VTC</t>
+          <t>WAM</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>VITTA CARE</t>
+          <t>WAMA DIAGNOSTICA</t>
         </is>
       </c>
       <c r="C1374" t="n">
@@ -34586,12 +34586,12 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>WAX</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>VITERNAT</t>
+          <t>WAX GREEN</t>
         </is>
       </c>
       <c r="C1375" t="n">
@@ -34611,12 +34611,12 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>WEA</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>VITAMINAS RACOES</t>
+          <t>WELLA</t>
         </is>
       </c>
       <c r="C1376" t="n">
@@ -34636,12 +34636,12 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>VTO</t>
+          <t>WES</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>VITTORE</t>
+          <t>WESP</t>
         </is>
       </c>
       <c r="C1377" t="n">
@@ -34661,12 +34661,12 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>VTT</t>
+          <t>WEV</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>VIT</t>
+          <t>WELLVIN ALIM</t>
         </is>
       </c>
       <c r="C1378" t="n">
@@ -34686,12 +34686,12 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>VTV</t>
+          <t>WPI</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>VITAVANT</t>
+          <t>WP LAB INDUST FARMACEUTICA</t>
         </is>
       </c>
       <c r="C1379" t="n">
@@ -34711,12 +34711,12 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>XSU</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>VITAMAX NUTRITION</t>
+          <t>X SUPERMERCADOS</t>
         </is>
       </c>
       <c r="C1380" t="n">
@@ -34736,12 +34736,12 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>VVA</t>
+          <t>YAH</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>VIVAI COSMETICOS</t>
+          <t>YAHWEH SHAMMAH IND</t>
         </is>
       </c>
       <c r="C1381" t="n">
@@ -34761,12 +34761,12 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>VVI</t>
+          <t>YAK</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>VIVAMIL</t>
+          <t>YAKULT CIA</t>
         </is>
       </c>
       <c r="C1382" t="n">
@@ -34786,12 +34786,12 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>YAM</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>VIVA REGENERA</t>
+          <t>YAMA CIA</t>
         </is>
       </c>
       <c r="C1383" t="n">
@@ -34811,12 +34811,12 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>WAM</t>
+          <t>YDR</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>WAMA DIAGNOSTICA</t>
+          <t>YDRA</t>
         </is>
       </c>
       <c r="C1384" t="n">
@@ -34836,12 +34836,12 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>WAX</t>
+          <t>YEN</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>WAX GREEN</t>
+          <t>YEN NUTRACEUTICA</t>
         </is>
       </c>
       <c r="C1385" t="n">
@@ -34861,12 +34861,12 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>WEA</t>
+          <t>YOE</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>WELLA</t>
+          <t>YOSEN</t>
         </is>
       </c>
       <c r="C1386" t="n">
@@ -34886,12 +34886,12 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>WES</t>
+          <t>YPY</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>WESP</t>
+          <t>YPY</t>
         </is>
       </c>
       <c r="C1387" t="n">
@@ -34911,12 +34911,12 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>WEV</t>
+          <t>Z2F</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>WELLVIN ALIM</t>
+          <t>Z2 FOODS</t>
         </is>
       </c>
       <c r="C1388" t="n">
@@ -34936,12 +34936,12 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>WPI</t>
+          <t>ZER</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>WP LAB INDUST FARMACEUTICA</t>
+          <t>ZEN ROOM</t>
         </is>
       </c>
       <c r="C1389" t="n">
@@ -34961,12 +34961,12 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>XSU</t>
+          <t>ZII</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>X SUPERMERCADOS</t>
+          <t>ZIIN ZIIN</t>
         </is>
       </c>
       <c r="C1390" t="n">
@@ -34986,12 +34986,12 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>YAH</t>
+          <t>ZIO</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>YAHWEH SHAMMAH IND</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="C1391" t="n">
@@ -35011,12 +35011,12 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>YAK</t>
+          <t>ZOE</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>YAKULT CIA</t>
+          <t>ZOETIS</t>
         </is>
       </c>
       <c r="C1392" t="n">
@@ -35036,12 +35036,12 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>YAM</t>
+          <t>ZUN</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>YAMA CIA</t>
+          <t>ZUNN</t>
         </is>
       </c>
       <c r="C1393" t="n">
@@ -35061,12 +35061,12 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>YDR</t>
+          <t>ZUR</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>YDRA</t>
+          <t>ZURI STRONG</t>
         </is>
       </c>
       <c r="C1394" t="n">
@@ -35086,12 +35086,12 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>YEN</t>
+          <t>ZYU</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>YEN NUTRACEUTICA</t>
+          <t>ZYDUS NIKKHO</t>
         </is>
       </c>
       <c r="C1395" t="n">
@@ -35108,258 +35108,8 @@
         </is>
       </c>
     </row>
-    <row r="1396">
-      <c r="A1396" t="inlineStr">
-        <is>
-          <t>YOE</t>
-        </is>
-      </c>
-      <c r="B1396" t="inlineStr">
-        <is>
-          <t>YOSEN</t>
-        </is>
-      </c>
-      <c r="C1396" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1396" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1396" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1397">
-      <c r="A1397" t="inlineStr">
-        <is>
-          <t>YPY</t>
-        </is>
-      </c>
-      <c r="B1397" t="inlineStr">
-        <is>
-          <t>YPY</t>
-        </is>
-      </c>
-      <c r="C1397" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1397" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1397" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1398">
-      <c r="A1398" t="inlineStr">
-        <is>
-          <t>Z2F</t>
-        </is>
-      </c>
-      <c r="B1398" t="inlineStr">
-        <is>
-          <t>Z2 FOODS</t>
-        </is>
-      </c>
-      <c r="C1398" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1398" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1398" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1399">
-      <c r="A1399" t="inlineStr">
-        <is>
-          <t>ZER</t>
-        </is>
-      </c>
-      <c r="B1399" t="inlineStr">
-        <is>
-          <t>ZEN ROOM</t>
-        </is>
-      </c>
-      <c r="C1399" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1399" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1399" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1400">
-      <c r="A1400" t="inlineStr">
-        <is>
-          <t>ZII</t>
-        </is>
-      </c>
-      <c r="B1400" t="inlineStr">
-        <is>
-          <t>ZIIN ZIIN</t>
-        </is>
-      </c>
-      <c r="C1400" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1400" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1400" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1401">
-      <c r="A1401" t="inlineStr">
-        <is>
-          <t>ZIO</t>
-        </is>
-      </c>
-      <c r="B1401" t="inlineStr">
-        <is>
-          <t>ZION</t>
-        </is>
-      </c>
-      <c r="C1401" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1401" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1401" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1402">
-      <c r="A1402" t="inlineStr">
-        <is>
-          <t>ZOE</t>
-        </is>
-      </c>
-      <c r="B1402" t="inlineStr">
-        <is>
-          <t>ZOETIS</t>
-        </is>
-      </c>
-      <c r="C1402" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1402" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1402" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1403">
-      <c r="A1403" t="inlineStr">
-        <is>
-          <t>ZUN</t>
-        </is>
-      </c>
-      <c r="B1403" t="inlineStr">
-        <is>
-          <t>ZUNN</t>
-        </is>
-      </c>
-      <c r="C1403" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1403" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1403" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1404">
-      <c r="A1404" t="inlineStr">
-        <is>
-          <t>ZUR</t>
-        </is>
-      </c>
-      <c r="B1404" t="inlineStr">
-        <is>
-          <t>ZURI STRONG</t>
-        </is>
-      </c>
-      <c r="C1404" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1404" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1404" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1405">
-      <c r="A1405" t="inlineStr">
-        <is>
-          <t>ZYU</t>
-        </is>
-      </c>
-      <c r="B1405" t="inlineStr">
-        <is>
-          <t>ZYDUS NIKKHO</t>
-        </is>
-      </c>
-      <c r="C1405" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1405" t="inlineStr">
-        <is>
-          <t>GERADA (conferir)</t>
-        </is>
-      </c>
-      <c r="E1405" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E1405"/>
+  <autoFilter ref="A1:E1395"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>